--- a/1000albums.xlsx
+++ b/1000albums.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelrodriguezmbp/Desktop/ytDown/top1000albums/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04927457-FD53-2646-8279-9E2386DB3B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C269F7-5DDC-494B-83C2-9CB81AAD18E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{0EA344FB-F653-8A4E-9162-CD1E4229299E}"/>
   </bookViews>
@@ -18,6 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Hoja2!$V$3:$V$163</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Hoja2!$V$3:$V$173</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Hoja2!$V$3:$V$163</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Hoja2!$V$3:$V$173</definedName>
     <definedName name="RangoDinamico" comment="para la grafica">DESREF(Hoja2!$V$3,0,0,Hoja2!$AF$3,1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="2845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="2883">
   <si>
     <t>The Grudge</t>
   </si>
@@ -11526,6 +11529,120 @@
   </si>
   <si>
     <t>r=0.132 · ≈ nula</t>
+  </si>
+  <si>
+    <t>TOP 25 (sin reglas)</t>
+  </si>
+  <si>
+    <t>Lateralus, 10,000 Days, Ænima, Fear Inoculum, Salival [LIVE]</t>
+  </si>
+  <si>
+    <t>Blackwater Park, Ghost Reveries, Deliverance, Still Life, Damnation</t>
+  </si>
+  <si>
+    <t>Fear of a Blank Planet, Deadwing, In Absentia</t>
+  </si>
+  <si>
+    <t>Wish You Were Here, The Dark Side Of The Moon, Animals, Meddle</t>
+  </si>
+  <si>
+    <t>In The Court Of The Crimson King, Red</t>
+  </si>
+  <si>
+    <t>Fear of a Blank Planet, Deadwing</t>
+  </si>
+  <si>
+    <t>In Rainbows, OK Computer, Kid A</t>
+  </si>
+  <si>
+    <t>In Rainbows, OK Computer, The Bends, A Moon Shaped Pool</t>
+  </si>
+  <si>
+    <t>Blackwater Park, Ghost Reveries, Deliverance, Still Life, Damnation, My Arms, Your Hearse</t>
+  </si>
+  <si>
+    <t>Even In The Quietest Moments..., Breakfast In America</t>
+  </si>
+  <si>
+    <t>Parachutes, X&amp;Y</t>
+  </si>
+  <si>
+    <t>Sgt. Pepper's Lonely Hearts Club Band, Abbey Road</t>
+  </si>
+  <si>
+    <t>The New Abnormal, Is This It</t>
+  </si>
+  <si>
+    <t>Velocity: Design: Comfort., You Will Never Know Why</t>
+  </si>
+  <si>
+    <t>Lateralus, 10,000 Days, Ænima, Salival [LIVE], Undertow</t>
+  </si>
+  <si>
+    <t>Lift Yr. Skinny Fists Like Antennas to Heaven!, F♯A♯∞</t>
+  </si>
+  <si>
+    <t>The Mantle, Ashes Against The Grain</t>
+  </si>
+  <si>
+    <t>Master Of Puppets, Ride The Lightning, …And Justice For All, Kill 'Em All</t>
+  </si>
+  <si>
+    <t>Rust In Peace, Megadeth</t>
+  </si>
+  <si>
+    <t>Kid A, The King Of Limbs</t>
+  </si>
+  <si>
+    <t>Discovery, Random Access Memories, Homework</t>
+  </si>
+  <si>
+    <t>Modal Soul, Metaphorical Music</t>
+  </si>
+  <si>
+    <t>TOP  Progressive Metal (26 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Progressive Rock (20 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Art Rock (16 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Alternative Rock (15 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Death Metal (8 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Pop Rock (8 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Indie Rock (8 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Dream Pop (7 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Alternative Metal (7 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Post Rock (7 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Shoegaze (7 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Post Metal (6 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Thrash Metal (6 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Electronic (5 álbumes)</t>
+  </si>
+  <si>
+    <t>TOP  Jazz Rap (5 álbumes)</t>
   </si>
 </sst>
 </file>
@@ -13482,7 +13599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="243">
+  <fills count="251">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -14935,6 +15052,54 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32BECE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0DB3E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FC5BA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF04B1ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF52C6B8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49C4BE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BBCD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1FB8DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -15118,7 +15283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="368">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -16187,6 +16352,30 @@
     <xf numFmtId="0" fontId="127" fillId="70" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="243" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="244" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="245" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="246" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="247" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="248" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="249" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="250" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25123,7 +25312,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -26284,24 +26473,24 @@
     <col min="14" max="14" width="12" style="3" customWidth="1"/>
     <col min="15" max="15" width="3.83203125" style="3" customWidth="1"/>
     <col min="16" max="17" width="3.6640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="4.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5" style="230" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5" style="230" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.5" style="230" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.83203125" style="230" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" style="230" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="53.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="75" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.5" style="230" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.33203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="52.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="28.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="29.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="30.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="43.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="42.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="13.33203125" style="3" customWidth="1"/>
     <col min="37" max="37" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -45378,7 +45567,7 @@
       <c r="AH232"/>
       <c r="AI232"/>
     </row>
-    <row r="233" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>1386</v>
       </c>
@@ -45414,11 +45603,13 @@
         <v>7</v>
       </c>
       <c r="O233" s="17"/>
-      <c r="R233"/>
-      <c r="S233"/>
-      <c r="T233"/>
-      <c r="U233"/>
-      <c r="V233"/>
+      <c r="R233" s="359" t="s">
+        <v>2845</v>
+      </c>
+      <c r="S233" s="359"/>
+      <c r="T233" s="359"/>
+      <c r="U233" s="359"/>
+      <c r="V233" s="359"/>
       <c r="W233"/>
       <c r="X233"/>
       <c r="Y233"/>
@@ -45465,11 +45656,21 @@
         <v>8</v>
       </c>
       <c r="O234" s="17"/>
-      <c r="R234"/>
-      <c r="S234"/>
-      <c r="T234"/>
-      <c r="U234"/>
-      <c r="V234"/>
+      <c r="R234" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S234" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T234" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U234" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V234" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W234"/>
       <c r="X234"/>
       <c r="Y234"/>
@@ -45521,11 +45722,21 @@
         <v>8.5</v>
       </c>
       <c r="O235" s="17"/>
-      <c r="R235"/>
-      <c r="S235"/>
-      <c r="T235"/>
-      <c r="U235"/>
-      <c r="V235"/>
+      <c r="R235" s="238">
+        <v>1</v>
+      </c>
+      <c r="S235" s="232" t="s">
+        <v>997</v>
+      </c>
+      <c r="T235" s="232" t="s">
+        <v>995</v>
+      </c>
+      <c r="U235" s="233">
+        <v>10.5</v>
+      </c>
+      <c r="V235" s="281">
+        <v>10.85</v>
+      </c>
       <c r="W235"/>
       <c r="X235"/>
       <c r="Y235"/>
@@ -45568,11 +45779,21 @@
         <v>7</v>
       </c>
       <c r="O236" s="17"/>
-      <c r="R236"/>
-      <c r="S236"/>
-      <c r="T236"/>
-      <c r="U236"/>
-      <c r="V236"/>
+      <c r="R236" s="240">
+        <v>2</v>
+      </c>
+      <c r="S236" s="235" t="s">
+        <v>326</v>
+      </c>
+      <c r="T236" s="235" t="s">
+        <v>7</v>
+      </c>
+      <c r="U236" s="236">
+        <v>9.89</v>
+      </c>
+      <c r="V236" s="281">
+        <v>10.52</v>
+      </c>
       <c r="W236"/>
       <c r="X236"/>
       <c r="Y236"/>
@@ -45625,11 +45846,21 @@
         <v>8</v>
       </c>
       <c r="O237" s="17"/>
-      <c r="R237"/>
-      <c r="S237"/>
-      <c r="T237"/>
-      <c r="U237"/>
-      <c r="V237"/>
+      <c r="R237" s="242">
+        <v>3</v>
+      </c>
+      <c r="S237" s="232" t="s">
+        <v>332</v>
+      </c>
+      <c r="T237" s="232" t="s">
+        <v>1028</v>
+      </c>
+      <c r="U237" s="233">
+        <v>10</v>
+      </c>
+      <c r="V237" s="281">
+        <v>10.39</v>
+      </c>
       <c r="W237"/>
       <c r="X237"/>
       <c r="Y237"/>
@@ -45680,11 +45911,21 @@
         <v>7.5</v>
       </c>
       <c r="O238" s="17"/>
-      <c r="R238"/>
-      <c r="S238"/>
-      <c r="T238"/>
-      <c r="U238"/>
-      <c r="V238"/>
+      <c r="R238" s="244">
+        <v>4</v>
+      </c>
+      <c r="S238" s="235" t="s">
+        <v>327</v>
+      </c>
+      <c r="T238" s="235" t="s">
+        <v>328</v>
+      </c>
+      <c r="U238" s="236">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="V238" s="281">
+        <v>10.37</v>
+      </c>
       <c r="W238"/>
       <c r="X238"/>
       <c r="Y238"/>
@@ -45731,11 +45972,21 @@
       <c r="M239" s="16"/>
       <c r="N239" s="16"/>
       <c r="O239" s="17"/>
-      <c r="R239"/>
-      <c r="S239"/>
-      <c r="T239"/>
-      <c r="U239"/>
-      <c r="V239"/>
+      <c r="R239" s="244">
+        <v>5</v>
+      </c>
+      <c r="S239" s="232" t="s">
+        <v>2702</v>
+      </c>
+      <c r="T239" s="232" t="s">
+        <v>674</v>
+      </c>
+      <c r="U239" s="233">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="V239" s="281">
+        <v>10.220000000000001</v>
+      </c>
       <c r="W239"/>
       <c r="X239"/>
       <c r="Y239"/>
@@ -45785,11 +46036,21 @@
         <v>8.93</v>
       </c>
       <c r="O240" s="17"/>
-      <c r="R240"/>
-      <c r="S240"/>
-      <c r="T240"/>
-      <c r="U240"/>
-      <c r="V240"/>
+      <c r="R240" s="244">
+        <v>6</v>
+      </c>
+      <c r="S240" s="235" t="s">
+        <v>332</v>
+      </c>
+      <c r="T240" s="235" t="s">
+        <v>333</v>
+      </c>
+      <c r="U240" s="236">
+        <v>9.61</v>
+      </c>
+      <c r="V240" s="281">
+        <v>10</v>
+      </c>
       <c r="W240"/>
       <c r="X240"/>
       <c r="Y240"/>
@@ -45840,11 +46101,21 @@
         <v>9.5</v>
       </c>
       <c r="O241" s="17"/>
-      <c r="R241"/>
-      <c r="S241"/>
-      <c r="T241"/>
-      <c r="U241"/>
-      <c r="V241"/>
+      <c r="R241" s="244">
+        <v>7</v>
+      </c>
+      <c r="S241" s="232" t="s">
+        <v>326</v>
+      </c>
+      <c r="T241" s="232" t="s">
+        <v>557</v>
+      </c>
+      <c r="U241" s="233">
+        <v>9.61</v>
+      </c>
+      <c r="V241" s="334">
+        <v>9.99</v>
+      </c>
       <c r="W241"/>
       <c r="X241"/>
       <c r="Y241"/>
@@ -45895,11 +46166,21 @@
         <v>8</v>
       </c>
       <c r="O242" s="17"/>
-      <c r="R242"/>
-      <c r="S242"/>
-      <c r="T242"/>
-      <c r="U242"/>
-      <c r="V242"/>
+      <c r="R242" s="244">
+        <v>8</v>
+      </c>
+      <c r="S242" s="235" t="s">
+        <v>326</v>
+      </c>
+      <c r="T242" s="235" t="s">
+        <v>158</v>
+      </c>
+      <c r="U242" s="236">
+        <v>9.61</v>
+      </c>
+      <c r="V242" s="333">
+        <v>9.9600000000000009</v>
+      </c>
       <c r="W242"/>
       <c r="X242"/>
       <c r="Y242"/>
@@ -45950,11 +46231,21 @@
         <v>10</v>
       </c>
       <c r="O243" s="17"/>
-      <c r="R243"/>
-      <c r="S243"/>
-      <c r="T243"/>
-      <c r="U243"/>
-      <c r="V243"/>
+      <c r="R243" s="244">
+        <v>9</v>
+      </c>
+      <c r="S243" s="232" t="s">
+        <v>327</v>
+      </c>
+      <c r="T243" s="232" t="s">
+        <v>329</v>
+      </c>
+      <c r="U243" s="233">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="V243" s="320">
+        <v>9.81</v>
+      </c>
       <c r="W243"/>
       <c r="X243"/>
       <c r="Y243"/>
@@ -46005,11 +46296,21 @@
         <v>8</v>
       </c>
       <c r="O244" s="17"/>
-      <c r="R244"/>
-      <c r="S244"/>
-      <c r="T244"/>
-      <c r="U244"/>
-      <c r="V244"/>
+      <c r="R244" s="244">
+        <v>10</v>
+      </c>
+      <c r="S244" s="235" t="s">
+        <v>326</v>
+      </c>
+      <c r="T244" s="235" t="s">
+        <v>1246</v>
+      </c>
+      <c r="U244" s="236">
+        <v>9.36</v>
+      </c>
+      <c r="V244" s="335">
+        <v>9.73</v>
+      </c>
       <c r="W244"/>
       <c r="X244"/>
       <c r="Y244"/>
@@ -46052,11 +46353,21 @@
         <v>9</v>
       </c>
       <c r="O245" s="17"/>
-      <c r="R245"/>
-      <c r="S245"/>
-      <c r="T245"/>
-      <c r="U245"/>
-      <c r="V245"/>
+      <c r="R245" s="244">
+        <v>11</v>
+      </c>
+      <c r="S245" s="232" t="s">
+        <v>332</v>
+      </c>
+      <c r="T245" s="232" t="s">
+        <v>768</v>
+      </c>
+      <c r="U245" s="233">
+        <v>9.4</v>
+      </c>
+      <c r="V245" s="317">
+        <v>9.5500000000000007</v>
+      </c>
       <c r="W245"/>
       <c r="X245"/>
       <c r="Y245"/>
@@ -46109,11 +46420,21 @@
         <v>8.5</v>
       </c>
       <c r="O246" s="17"/>
-      <c r="R246"/>
-      <c r="S246"/>
-      <c r="T246"/>
-      <c r="U246"/>
-      <c r="V246"/>
+      <c r="R246" s="244">
+        <v>12</v>
+      </c>
+      <c r="S246" s="235" t="s">
+        <v>330</v>
+      </c>
+      <c r="T246" s="235" t="s">
+        <v>269</v>
+      </c>
+      <c r="U246" s="236">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="V246" s="300">
+        <v>9.5299999999999994</v>
+      </c>
       <c r="W246"/>
       <c r="X246"/>
       <c r="Y246"/>
@@ -46164,11 +46485,21 @@
         <v>9.5</v>
       </c>
       <c r="O247" s="17"/>
-      <c r="R247"/>
-      <c r="S247"/>
-      <c r="T247"/>
-      <c r="U247"/>
-      <c r="V247"/>
+      <c r="R247" s="244">
+        <v>13</v>
+      </c>
+      <c r="S247" s="232" t="s">
+        <v>326</v>
+      </c>
+      <c r="T247" s="232" t="s">
+        <v>2574</v>
+      </c>
+      <c r="U247" s="233">
+        <v>9.25</v>
+      </c>
+      <c r="V247" s="300">
+        <v>9.5299999999999994</v>
+      </c>
       <c r="W247"/>
       <c r="X247"/>
       <c r="Y247"/>
@@ -46215,11 +46546,21 @@
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
       <c r="O248" s="17"/>
-      <c r="R248"/>
-      <c r="S248"/>
-      <c r="T248"/>
-      <c r="U248"/>
-      <c r="V248"/>
+      <c r="R248" s="244">
+        <v>14</v>
+      </c>
+      <c r="S248" s="235" t="s">
+        <v>331</v>
+      </c>
+      <c r="T248" s="235" t="s">
+        <v>1184</v>
+      </c>
+      <c r="U248" s="236">
+        <v>9.4</v>
+      </c>
+      <c r="V248" s="296">
+        <v>9.4600000000000009</v>
+      </c>
       <c r="W248"/>
       <c r="X248"/>
       <c r="Y248"/>
@@ -46271,11 +46612,21 @@
         <v>8.67</v>
       </c>
       <c r="O249" s="17"/>
-      <c r="R249"/>
-      <c r="S249"/>
-      <c r="T249"/>
-      <c r="U249"/>
-      <c r="V249"/>
+      <c r="R249" s="244">
+        <v>15</v>
+      </c>
+      <c r="S249" s="232" t="s">
+        <v>2039</v>
+      </c>
+      <c r="T249" s="232" t="s">
+        <v>2032</v>
+      </c>
+      <c r="U249" s="233">
+        <v>9.31</v>
+      </c>
+      <c r="V249" s="253">
+        <v>9.43</v>
+      </c>
       <c r="W249"/>
       <c r="X249"/>
       <c r="Y249"/>
@@ -46324,11 +46675,21 @@
         <v>10</v>
       </c>
       <c r="O250" s="17"/>
-      <c r="R250"/>
-      <c r="S250"/>
-      <c r="T250"/>
-      <c r="U250"/>
-      <c r="V250"/>
+      <c r="R250" s="244">
+        <v>16</v>
+      </c>
+      <c r="S250" s="235" t="s">
+        <v>2491</v>
+      </c>
+      <c r="T250" s="235" t="s">
+        <v>2475</v>
+      </c>
+      <c r="U250" s="236">
+        <v>9.33</v>
+      </c>
+      <c r="V250" s="337">
+        <v>9.3800000000000008</v>
+      </c>
       <c r="W250"/>
       <c r="X250"/>
       <c r="Y250"/>
@@ -46375,11 +46736,21 @@
         <v>9</v>
       </c>
       <c r="O251" s="17"/>
-      <c r="R251"/>
-      <c r="S251"/>
-      <c r="T251"/>
-      <c r="U251"/>
-      <c r="V251"/>
+      <c r="R251" s="244">
+        <v>17</v>
+      </c>
+      <c r="S251" s="232" t="s">
+        <v>335</v>
+      </c>
+      <c r="T251" s="232" t="s">
+        <v>56</v>
+      </c>
+      <c r="U251" s="233">
+        <v>9.25</v>
+      </c>
+      <c r="V251" s="305">
+        <v>9.3699999999999992</v>
+      </c>
       <c r="W251"/>
       <c r="X251"/>
       <c r="Y251"/>
@@ -46431,11 +46802,21 @@
         <v>8.5</v>
       </c>
       <c r="O252" s="17"/>
-      <c r="R252"/>
-      <c r="S252"/>
-      <c r="T252"/>
-      <c r="U252"/>
-      <c r="V252"/>
+      <c r="R252" s="244">
+        <v>18</v>
+      </c>
+      <c r="S252" s="235" t="s">
+        <v>327</v>
+      </c>
+      <c r="T252" s="235" t="s">
+        <v>285</v>
+      </c>
+      <c r="U252" s="236">
+        <v>9.15</v>
+      </c>
+      <c r="V252" s="305">
+        <v>9.3699999999999992</v>
+      </c>
       <c r="W252"/>
       <c r="X252"/>
       <c r="Y252"/>
@@ -46482,11 +46863,21 @@
         <v>8</v>
       </c>
       <c r="O253" s="17"/>
-      <c r="R253"/>
-      <c r="S253"/>
-      <c r="T253"/>
-      <c r="U253"/>
-      <c r="V253"/>
+      <c r="R253" s="244">
+        <v>19</v>
+      </c>
+      <c r="S253" s="232" t="s">
+        <v>331</v>
+      </c>
+      <c r="T253" s="232" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U253" s="233">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="V253" s="297">
+        <v>9.36</v>
+      </c>
       <c r="W253"/>
       <c r="X253"/>
       <c r="Y253"/>
@@ -46538,11 +46929,21 @@
         <v>10.5</v>
       </c>
       <c r="O254" s="17"/>
-      <c r="R254"/>
-      <c r="S254"/>
-      <c r="T254"/>
-      <c r="U254"/>
-      <c r="V254"/>
+      <c r="R254" s="244">
+        <v>20</v>
+      </c>
+      <c r="S254" s="235" t="s">
+        <v>336</v>
+      </c>
+      <c r="T254" s="235" t="s">
+        <v>188</v>
+      </c>
+      <c r="U254" s="236">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="V254" s="287">
+        <v>9.34</v>
+      </c>
       <c r="W254"/>
       <c r="X254"/>
       <c r="Y254"/>
@@ -46593,11 +46994,21 @@
         <v>9.5</v>
       </c>
       <c r="O255" s="17"/>
-      <c r="R255"/>
-      <c r="S255"/>
-      <c r="T255"/>
-      <c r="U255"/>
-      <c r="V255"/>
+      <c r="R255" s="244">
+        <v>21</v>
+      </c>
+      <c r="S255" s="232" t="s">
+        <v>334</v>
+      </c>
+      <c r="T255" s="232" t="s">
+        <v>132</v>
+      </c>
+      <c r="U255" s="233">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="V255" s="311">
+        <v>9.2799999999999994</v>
+      </c>
       <c r="W255"/>
       <c r="X255"/>
       <c r="Y255"/>
@@ -46648,11 +47059,21 @@
         <v>8</v>
       </c>
       <c r="O256" s="17"/>
-      <c r="R256"/>
-      <c r="S256"/>
-      <c r="T256"/>
-      <c r="U256"/>
-      <c r="V256"/>
+      <c r="R256" s="244">
+        <v>22</v>
+      </c>
+      <c r="S256" s="235" t="s">
+        <v>444</v>
+      </c>
+      <c r="T256" s="235" t="s">
+        <v>36</v>
+      </c>
+      <c r="U256" s="236">
+        <v>9.15</v>
+      </c>
+      <c r="V256" s="319">
+        <v>9.23</v>
+      </c>
       <c r="W256"/>
       <c r="X256"/>
       <c r="Y256"/>
@@ -46699,11 +47120,21 @@
         <v>10.5</v>
       </c>
       <c r="O257" s="17"/>
-      <c r="R257"/>
-      <c r="S257"/>
-      <c r="T257"/>
-      <c r="U257"/>
-      <c r="V257"/>
+      <c r="R257" s="244">
+        <v>23</v>
+      </c>
+      <c r="S257" s="232" t="s">
+        <v>480</v>
+      </c>
+      <c r="T257" s="232" t="s">
+        <v>498</v>
+      </c>
+      <c r="U257" s="233">
+        <v>9.17</v>
+      </c>
+      <c r="V257" s="319">
+        <v>9.23</v>
+      </c>
       <c r="W257"/>
       <c r="X257"/>
       <c r="Y257"/>
@@ -46755,11 +47186,21 @@
         <v>10.5</v>
       </c>
       <c r="O258" s="17"/>
-      <c r="R258"/>
-      <c r="S258"/>
-      <c r="T258"/>
-      <c r="U258"/>
-      <c r="V258"/>
+      <c r="R258" s="244">
+        <v>24</v>
+      </c>
+      <c r="S258" s="235" t="s">
+        <v>335</v>
+      </c>
+      <c r="T258" s="235" t="s">
+        <v>693</v>
+      </c>
+      <c r="U258" s="236">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="V258" s="306">
+        <v>9.2100000000000009</v>
+      </c>
       <c r="W258"/>
       <c r="X258"/>
       <c r="Y258"/>
@@ -46802,11 +47243,21 @@
         <v>9</v>
       </c>
       <c r="O259" s="17"/>
-      <c r="R259"/>
-      <c r="S259"/>
-      <c r="T259"/>
-      <c r="U259"/>
-      <c r="V259"/>
+      <c r="R259" s="244">
+        <v>25</v>
+      </c>
+      <c r="S259" s="232" t="s">
+        <v>337</v>
+      </c>
+      <c r="T259" s="232" t="s">
+        <v>2573</v>
+      </c>
+      <c r="U259" s="233">
+        <v>9.08</v>
+      </c>
+      <c r="V259" s="265">
+        <v>9.17</v>
+      </c>
       <c r="W259"/>
       <c r="X259"/>
       <c r="Y259"/>
@@ -47038,7 +47489,7 @@
       <c r="AH263"/>
       <c r="AI263"/>
     </row>
-    <row r="264" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>1601</v>
       </c>
@@ -47071,11 +47522,13 @@
         <v>8</v>
       </c>
       <c r="O264" s="17"/>
-      <c r="R264"/>
-      <c r="S264"/>
-      <c r="T264"/>
-      <c r="U264"/>
-      <c r="V264"/>
+      <c r="R264" s="359" t="s">
+        <v>2868</v>
+      </c>
+      <c r="S264" s="359"/>
+      <c r="T264" s="359"/>
+      <c r="U264" s="359"/>
+      <c r="V264" s="359"/>
       <c r="W264"/>
       <c r="X264"/>
       <c r="Y264"/>
@@ -47123,11 +47576,21 @@
         <v>9</v>
       </c>
       <c r="O265" s="17"/>
-      <c r="R265"/>
-      <c r="S265"/>
-      <c r="T265"/>
-      <c r="U265"/>
-      <c r="V265"/>
+      <c r="R265" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S265" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T265" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U265" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V265" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W265"/>
       <c r="X265"/>
       <c r="Y265"/>
@@ -47179,11 +47642,21 @@
         <v>8</v>
       </c>
       <c r="O266" s="17"/>
-      <c r="R266"/>
-      <c r="S266"/>
-      <c r="T266"/>
-      <c r="U266"/>
-      <c r="V266"/>
+      <c r="R266" s="238">
+        <v>1</v>
+      </c>
+      <c r="S266" s="232" t="s">
+        <v>326</v>
+      </c>
+      <c r="T266" s="232" t="s">
+        <v>2846</v>
+      </c>
+      <c r="U266" s="233">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="V266" s="363">
+        <v>9.9499999999999993</v>
+      </c>
       <c r="W266"/>
       <c r="X266"/>
       <c r="Y266"/>
@@ -47234,11 +47707,21 @@
         <v>7.5</v>
       </c>
       <c r="O267" s="17"/>
-      <c r="R267"/>
-      <c r="S267"/>
-      <c r="T267"/>
-      <c r="U267"/>
-      <c r="V267"/>
+      <c r="R267" s="240">
+        <v>2</v>
+      </c>
+      <c r="S267" s="235" t="s">
+        <v>334</v>
+      </c>
+      <c r="T267" s="235" t="s">
+        <v>2847</v>
+      </c>
+      <c r="U267" s="236">
+        <v>8.92</v>
+      </c>
+      <c r="V267" s="328">
+        <v>8.93</v>
+      </c>
       <c r="W267"/>
       <c r="X267"/>
       <c r="Y267"/>
@@ -47289,11 +47772,21 @@
         <v>8</v>
       </c>
       <c r="O268" s="17"/>
-      <c r="R268"/>
-      <c r="S268"/>
-      <c r="T268"/>
-      <c r="U268"/>
-      <c r="V268"/>
+      <c r="R268" s="242">
+        <v>3</v>
+      </c>
+      <c r="S268" s="232" t="s">
+        <v>480</v>
+      </c>
+      <c r="T268" s="232" t="s">
+        <v>2848</v>
+      </c>
+      <c r="U268" s="233">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="V268" s="364">
+        <v>9.0299999999999994</v>
+      </c>
       <c r="W268"/>
       <c r="X268"/>
       <c r="Y268"/>
@@ -47344,11 +47837,21 @@
         <v>7.5</v>
       </c>
       <c r="O269" s="17"/>
-      <c r="R269"/>
-      <c r="S269"/>
-      <c r="T269"/>
-      <c r="U269"/>
-      <c r="V269"/>
+      <c r="R269" s="244">
+        <v>4</v>
+      </c>
+      <c r="S269" s="235" t="s">
+        <v>1525</v>
+      </c>
+      <c r="T269" s="235" t="s">
+        <v>1526</v>
+      </c>
+      <c r="U269" s="236">
+        <v>8.82</v>
+      </c>
+      <c r="V269" s="275">
+        <v>8.84</v>
+      </c>
       <c r="W269"/>
       <c r="X269"/>
       <c r="Y269"/>
@@ -47399,11 +47902,21 @@
         <v>7.5</v>
       </c>
       <c r="O270" s="17"/>
-      <c r="R270"/>
-      <c r="S270"/>
-      <c r="T270"/>
-      <c r="U270"/>
-      <c r="V270"/>
+      <c r="R270" s="244">
+        <v>5</v>
+      </c>
+      <c r="S270" s="232" t="s">
+        <v>1282</v>
+      </c>
+      <c r="T270" s="232" t="s">
+        <v>1283</v>
+      </c>
+      <c r="U270" s="233">
+        <v>8.67</v>
+      </c>
+      <c r="V270" s="267">
+        <v>8.7899999999999991</v>
+      </c>
       <c r="W270"/>
       <c r="X270"/>
       <c r="Y270"/>
@@ -47465,7 +47978,7 @@
       <c r="AH271"/>
       <c r="AI271"/>
     </row>
-    <row r="272" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="137" t="s">
         <v>1654</v>
       </c>
@@ -47502,11 +48015,13 @@
         <v>9</v>
       </c>
       <c r="O272" s="17"/>
-      <c r="R272"/>
-      <c r="S272"/>
-      <c r="T272"/>
-      <c r="U272"/>
-      <c r="V272"/>
+      <c r="R272" s="359" t="s">
+        <v>2869</v>
+      </c>
+      <c r="S272" s="359"/>
+      <c r="T272" s="359"/>
+      <c r="U272" s="359"/>
+      <c r="V272" s="359"/>
       <c r="W272"/>
       <c r="X272"/>
       <c r="Y272"/>
@@ -47557,11 +48072,21 @@
         <v>10</v>
       </c>
       <c r="O273" s="17"/>
-      <c r="R273"/>
-      <c r="S273"/>
-      <c r="T273"/>
-      <c r="U273"/>
-      <c r="V273"/>
+      <c r="R273" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S273" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T273" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U273" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V273" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W273"/>
       <c r="X273"/>
       <c r="Y273"/>
@@ -47612,11 +48137,21 @@
         <v>9</v>
       </c>
       <c r="O274" s="17"/>
-      <c r="R274"/>
-      <c r="S274"/>
-      <c r="T274"/>
-      <c r="U274"/>
-      <c r="V274"/>
+      <c r="R274" s="238">
+        <v>1</v>
+      </c>
+      <c r="S274" s="232" t="s">
+        <v>332</v>
+      </c>
+      <c r="T274" s="232" t="s">
+        <v>2849</v>
+      </c>
+      <c r="U274" s="233">
+        <v>9.48</v>
+      </c>
+      <c r="V274" s="335">
+        <v>9.73</v>
+      </c>
       <c r="W274"/>
       <c r="X274"/>
       <c r="Y274"/>
@@ -47659,11 +48194,21 @@
         <v>9</v>
       </c>
       <c r="O275" s="17"/>
-      <c r="R275"/>
-      <c r="S275"/>
-      <c r="T275"/>
-      <c r="U275"/>
-      <c r="V275"/>
+      <c r="R275" s="240">
+        <v>2</v>
+      </c>
+      <c r="S275" s="235" t="s">
+        <v>331</v>
+      </c>
+      <c r="T275" s="235" t="s">
+        <v>2850</v>
+      </c>
+      <c r="U275" s="236">
+        <v>9.35</v>
+      </c>
+      <c r="V275" s="360">
+        <v>9.41</v>
+      </c>
       <c r="W275"/>
       <c r="X275"/>
       <c r="Y275"/>
@@ -47712,11 +48257,21 @@
       <c r="M276" s="2"/>
       <c r="N276" s="2"/>
       <c r="O276" s="17"/>
-      <c r="R276"/>
-      <c r="S276"/>
-      <c r="T276"/>
-      <c r="U276"/>
-      <c r="V276"/>
+      <c r="R276" s="242">
+        <v>3</v>
+      </c>
+      <c r="S276" s="232" t="s">
+        <v>2491</v>
+      </c>
+      <c r="T276" s="232" t="s">
+        <v>2475</v>
+      </c>
+      <c r="U276" s="233">
+        <v>9.33</v>
+      </c>
+      <c r="V276" s="337">
+        <v>9.3800000000000008</v>
+      </c>
       <c r="W276"/>
       <c r="X276"/>
       <c r="Y276"/>
@@ -47764,11 +48319,21 @@
         <v>8.4</v>
       </c>
       <c r="O277" s="17"/>
-      <c r="R277"/>
-      <c r="S277"/>
-      <c r="T277"/>
-      <c r="U277"/>
-      <c r="V277"/>
+      <c r="R277" s="244">
+        <v>4</v>
+      </c>
+      <c r="S277" s="235" t="s">
+        <v>444</v>
+      </c>
+      <c r="T277" s="235" t="s">
+        <v>36</v>
+      </c>
+      <c r="U277" s="236">
+        <v>9.15</v>
+      </c>
+      <c r="V277" s="319">
+        <v>9.23</v>
+      </c>
       <c r="W277"/>
       <c r="X277"/>
       <c r="Y277"/>
@@ -47816,11 +48381,21 @@
         <v>8</v>
       </c>
       <c r="O278" s="17"/>
-      <c r="R278"/>
-      <c r="S278"/>
-      <c r="T278"/>
-      <c r="U278"/>
-      <c r="V278"/>
+      <c r="R278" s="244">
+        <v>5</v>
+      </c>
+      <c r="S278" s="232" t="s">
+        <v>480</v>
+      </c>
+      <c r="T278" s="232" t="s">
+        <v>2851</v>
+      </c>
+      <c r="U278" s="233">
+        <v>9.06</v>
+      </c>
+      <c r="V278" s="365">
+        <v>9.14</v>
+      </c>
       <c r="W278"/>
       <c r="X278"/>
       <c r="Y278"/>
@@ -47889,7 +48464,7 @@
       <c r="AH279"/>
       <c r="AI279"/>
     </row>
-    <row r="280" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
         <v>1707</v>
       </c>
@@ -47923,11 +48498,13 @@
         <v>8</v>
       </c>
       <c r="O280" s="17"/>
-      <c r="R280"/>
-      <c r="S280"/>
-      <c r="T280"/>
-      <c r="U280"/>
-      <c r="V280"/>
+      <c r="R280" s="359" t="s">
+        <v>2870</v>
+      </c>
+      <c r="S280" s="359"/>
+      <c r="T280" s="359"/>
+      <c r="U280" s="359"/>
+      <c r="V280" s="359"/>
       <c r="W280"/>
       <c r="X280"/>
       <c r="Y280"/>
@@ -47978,11 +48555,21 @@
         <v>8.5</v>
       </c>
       <c r="O281" s="17"/>
-      <c r="R281"/>
-      <c r="S281"/>
-      <c r="T281"/>
-      <c r="U281"/>
-      <c r="V281"/>
+      <c r="R281" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S281" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T281" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U281" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V281" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W281"/>
       <c r="X281"/>
       <c r="Y281"/>
@@ -48033,11 +48620,21 @@
         <v>10</v>
       </c>
       <c r="O282" s="17"/>
-      <c r="R282"/>
-      <c r="S282"/>
-      <c r="T282"/>
-      <c r="U282"/>
-      <c r="V282"/>
+      <c r="R282" s="238">
+        <v>1</v>
+      </c>
+      <c r="S282" s="232" t="s">
+        <v>332</v>
+      </c>
+      <c r="T282" s="232" t="s">
+        <v>1028</v>
+      </c>
+      <c r="U282" s="233">
+        <v>10</v>
+      </c>
+      <c r="V282" s="281">
+        <v>10.39</v>
+      </c>
       <c r="W282"/>
       <c r="X282"/>
       <c r="Y282"/>
@@ -48084,11 +48681,21 @@
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
       <c r="O283" s="17"/>
-      <c r="R283"/>
-      <c r="S283"/>
-      <c r="T283"/>
-      <c r="U283"/>
-      <c r="V283"/>
+      <c r="R283" s="240">
+        <v>2</v>
+      </c>
+      <c r="S283" s="235" t="s">
+        <v>327</v>
+      </c>
+      <c r="T283" s="235" t="s">
+        <v>2852</v>
+      </c>
+      <c r="U283" s="236">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="V283" s="361">
+        <v>9.85</v>
+      </c>
       <c r="W283"/>
       <c r="X283"/>
       <c r="Y283"/>
@@ -48140,11 +48747,21 @@
         <v>8.91</v>
       </c>
       <c r="O284" s="17"/>
-      <c r="R284"/>
-      <c r="S284"/>
-      <c r="T284"/>
-      <c r="U284"/>
-      <c r="V284"/>
+      <c r="R284" s="242">
+        <v>3</v>
+      </c>
+      <c r="S284" s="232" t="s">
+        <v>331</v>
+      </c>
+      <c r="T284" s="232" t="s">
+        <v>2850</v>
+      </c>
+      <c r="U284" s="233">
+        <v>9.35</v>
+      </c>
+      <c r="V284" s="360">
+        <v>9.41</v>
+      </c>
       <c r="W284"/>
       <c r="X284"/>
       <c r="Y284"/>
@@ -48191,11 +48808,21 @@
         <v>9</v>
       </c>
       <c r="O285" s="17"/>
-      <c r="R285"/>
-      <c r="S285"/>
-      <c r="T285"/>
-      <c r="U285"/>
-      <c r="V285"/>
+      <c r="R285" s="244">
+        <v>4</v>
+      </c>
+      <c r="S285" s="235" t="s">
+        <v>444</v>
+      </c>
+      <c r="T285" s="235" t="s">
+        <v>36</v>
+      </c>
+      <c r="U285" s="236">
+        <v>9.15</v>
+      </c>
+      <c r="V285" s="319">
+        <v>9.23</v>
+      </c>
       <c r="W285"/>
       <c r="X285"/>
       <c r="Y285"/>
@@ -48247,11 +48874,21 @@
         <v>9.5</v>
       </c>
       <c r="O286" s="17"/>
-      <c r="R286"/>
-      <c r="S286"/>
-      <c r="T286"/>
-      <c r="U286"/>
-      <c r="V286"/>
+      <c r="R286" s="244">
+        <v>5</v>
+      </c>
+      <c r="S286" s="232" t="s">
+        <v>1336</v>
+      </c>
+      <c r="T286" s="232" t="s">
+        <v>1327</v>
+      </c>
+      <c r="U286" s="233">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="V286" s="256">
+        <v>8.91</v>
+      </c>
       <c r="W286"/>
       <c r="X286"/>
       <c r="Y286"/>
@@ -48313,7 +48950,7 @@
       <c r="AH287"/>
       <c r="AI287"/>
     </row>
-    <row r="288" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>1715</v>
       </c>
@@ -48351,11 +48988,13 @@
         <v>8.5</v>
       </c>
       <c r="O288" s="17"/>
-      <c r="R288"/>
-      <c r="S288"/>
-      <c r="T288"/>
-      <c r="U288"/>
-      <c r="V288"/>
+      <c r="R288" s="359" t="s">
+        <v>2871</v>
+      </c>
+      <c r="S288" s="359"/>
+      <c r="T288" s="359"/>
+      <c r="U288" s="359"/>
+      <c r="V288" s="359"/>
       <c r="W288"/>
       <c r="X288"/>
       <c r="Y288"/>
@@ -48406,11 +49045,21 @@
         <v>8.5</v>
       </c>
       <c r="O289" s="17"/>
-      <c r="R289"/>
-      <c r="S289"/>
-      <c r="T289"/>
-      <c r="U289"/>
-      <c r="V289"/>
+      <c r="R289" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S289" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T289" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U289" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V289" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W289"/>
       <c r="X289"/>
       <c r="Y289"/>
@@ -48461,11 +49110,21 @@
         <v>9</v>
       </c>
       <c r="O290" s="17"/>
-      <c r="R290"/>
-      <c r="S290"/>
-      <c r="T290"/>
-      <c r="U290"/>
-      <c r="V290"/>
+      <c r="R290" s="238">
+        <v>1</v>
+      </c>
+      <c r="S290" s="232" t="s">
+        <v>327</v>
+      </c>
+      <c r="T290" s="232" t="s">
+        <v>2853</v>
+      </c>
+      <c r="U290" s="233">
+        <v>9.25</v>
+      </c>
+      <c r="V290" s="366">
+        <v>9.49</v>
+      </c>
       <c r="W290"/>
       <c r="X290"/>
       <c r="Y290"/>
@@ -48516,11 +49175,21 @@
         <v>8</v>
       </c>
       <c r="O291" s="17"/>
-      <c r="R291"/>
-      <c r="S291"/>
-      <c r="T291"/>
-      <c r="U291"/>
-      <c r="V291"/>
+      <c r="R291" s="240">
+        <v>2</v>
+      </c>
+      <c r="S291" s="235" t="s">
+        <v>717</v>
+      </c>
+      <c r="T291" s="235" t="s">
+        <v>1430</v>
+      </c>
+      <c r="U291" s="236">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="V291" s="255">
+        <v>8.89</v>
+      </c>
       <c r="W291"/>
       <c r="X291"/>
       <c r="Y291"/>
@@ -48571,11 +49240,21 @@
         <v>10</v>
       </c>
       <c r="O292" s="17"/>
-      <c r="R292"/>
-      <c r="S292"/>
-      <c r="T292"/>
-      <c r="U292"/>
-      <c r="V292"/>
+      <c r="R292" s="242">
+        <v>3</v>
+      </c>
+      <c r="S292" s="232" t="s">
+        <v>2597</v>
+      </c>
+      <c r="T292" s="232" t="s">
+        <v>2598</v>
+      </c>
+      <c r="U292" s="233">
+        <v>8.86</v>
+      </c>
+      <c r="V292" s="258">
+        <v>8.8800000000000008</v>
+      </c>
       <c r="W292"/>
       <c r="X292"/>
       <c r="Y292"/>
@@ -48626,11 +49305,21 @@
         <v>8</v>
       </c>
       <c r="O293" s="17"/>
-      <c r="R293"/>
-      <c r="S293"/>
-      <c r="T293"/>
-      <c r="U293"/>
-      <c r="V293"/>
+      <c r="R293" s="244">
+        <v>4</v>
+      </c>
+      <c r="S293" s="235" t="s">
+        <v>2426</v>
+      </c>
+      <c r="T293" s="235" t="s">
+        <v>2416</v>
+      </c>
+      <c r="U293" s="236">
+        <v>8.86</v>
+      </c>
+      <c r="V293" s="291">
+        <v>8.74</v>
+      </c>
       <c r="W293"/>
       <c r="X293"/>
       <c r="Y293"/>
@@ -48681,11 +49370,21 @@
         <v>8.5</v>
       </c>
       <c r="O294" s="17"/>
-      <c r="R294"/>
-      <c r="S294"/>
-      <c r="T294"/>
-      <c r="U294"/>
-      <c r="V294"/>
+      <c r="R294" s="244">
+        <v>5</v>
+      </c>
+      <c r="S294" s="232" t="s">
+        <v>1337</v>
+      </c>
+      <c r="T294" s="232" t="s">
+        <v>1338</v>
+      </c>
+      <c r="U294" s="233">
+        <v>8.77</v>
+      </c>
+      <c r="V294" s="280">
+        <v>8.65</v>
+      </c>
       <c r="W294"/>
       <c r="X294"/>
       <c r="Y294"/>
@@ -48747,7 +49446,7 @@
       <c r="AH295"/>
       <c r="AI295"/>
     </row>
-    <row r="296" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>1723</v>
       </c>
@@ -48781,11 +49480,13 @@
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
       <c r="O296" s="17"/>
-      <c r="R296"/>
-      <c r="S296"/>
-      <c r="T296"/>
-      <c r="U296"/>
-      <c r="V296"/>
+      <c r="R296" s="359" t="s">
+        <v>2872</v>
+      </c>
+      <c r="S296" s="359"/>
+      <c r="T296" s="359"/>
+      <c r="U296" s="359"/>
+      <c r="V296" s="359"/>
       <c r="W296"/>
       <c r="X296"/>
       <c r="Y296"/>
@@ -48837,11 +49538,21 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="O297" s="17"/>
-      <c r="R297"/>
-      <c r="S297"/>
-      <c r="T297"/>
-      <c r="U297"/>
-      <c r="V297"/>
+      <c r="R297" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S297" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T297" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U297" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V297" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W297"/>
       <c r="X297"/>
       <c r="Y297"/>
@@ -48888,11 +49599,21 @@
         <v>8</v>
       </c>
       <c r="O298" s="17"/>
-      <c r="R298"/>
-      <c r="S298"/>
-      <c r="T298"/>
-      <c r="U298"/>
-      <c r="V298"/>
+      <c r="R298" s="238">
+        <v>1</v>
+      </c>
+      <c r="S298" s="232" t="s">
+        <v>334</v>
+      </c>
+      <c r="T298" s="232" t="s">
+        <v>2854</v>
+      </c>
+      <c r="U298" s="233">
+        <v>8.81</v>
+      </c>
+      <c r="V298" s="340">
+        <v>8.82</v>
+      </c>
       <c r="W298"/>
       <c r="X298"/>
       <c r="Y298"/>
@@ -48944,11 +49665,21 @@
         <v>7.5</v>
       </c>
       <c r="O299" s="17"/>
-      <c r="R299"/>
-      <c r="S299"/>
-      <c r="T299"/>
-      <c r="U299"/>
-      <c r="V299"/>
+      <c r="R299" s="240">
+        <v>2</v>
+      </c>
+      <c r="S299" s="235" t="s">
+        <v>1525</v>
+      </c>
+      <c r="T299" s="235" t="s">
+        <v>1526</v>
+      </c>
+      <c r="U299" s="236">
+        <v>8.82</v>
+      </c>
+      <c r="V299" s="275">
+        <v>8.84</v>
+      </c>
       <c r="W299"/>
       <c r="X299"/>
       <c r="Y299"/>
@@ -48997,11 +49728,21 @@
         <v>9</v>
       </c>
       <c r="O300" s="17"/>
-      <c r="R300"/>
-      <c r="S300"/>
-      <c r="T300"/>
-      <c r="U300"/>
-      <c r="V300"/>
+      <c r="R300" s="242">
+        <v>3</v>
+      </c>
+      <c r="S300" s="232" t="s">
+        <v>769</v>
+      </c>
+      <c r="T300" s="232" t="s">
+        <v>770</v>
+      </c>
+      <c r="U300" s="233">
+        <v>8.67</v>
+      </c>
+      <c r="V300" s="254">
+        <v>8.57</v>
+      </c>
       <c r="W300"/>
       <c r="X300"/>
       <c r="Y300"/>
@@ -49175,7 +49916,7 @@
       <c r="AH303"/>
       <c r="AI303"/>
     </row>
-    <row r="304" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>1730</v>
       </c>
@@ -49212,11 +49953,13 @@
         <v>9</v>
       </c>
       <c r="O304" s="17"/>
-      <c r="R304"/>
-      <c r="S304"/>
-      <c r="T304"/>
-      <c r="U304"/>
-      <c r="V304"/>
+      <c r="R304" s="359" t="s">
+        <v>2873</v>
+      </c>
+      <c r="S304" s="359"/>
+      <c r="T304" s="359"/>
+      <c r="U304" s="359"/>
+      <c r="V304" s="359"/>
       <c r="W304"/>
       <c r="X304"/>
       <c r="Y304"/>
@@ -49263,11 +50006,21 @@
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
       <c r="O305" s="17"/>
-      <c r="R305"/>
-      <c r="S305"/>
-      <c r="T305"/>
-      <c r="U305"/>
-      <c r="V305"/>
+      <c r="R305" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S305" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T305" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U305" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V305" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W305"/>
       <c r="X305"/>
       <c r="Y305"/>
@@ -49319,11 +50072,21 @@
         <v>8.6</v>
       </c>
       <c r="O306" s="17"/>
-      <c r="R306"/>
-      <c r="S306"/>
-      <c r="T306"/>
-      <c r="U306"/>
-      <c r="V306"/>
+      <c r="R306" s="238">
+        <v>1</v>
+      </c>
+      <c r="S306" s="232" t="s">
+        <v>1608</v>
+      </c>
+      <c r="T306" s="232" t="s">
+        <v>2855</v>
+      </c>
+      <c r="U306" s="233">
+        <v>8.91</v>
+      </c>
+      <c r="V306" s="340">
+        <v>8.82</v>
+      </c>
       <c r="W306"/>
       <c r="X306"/>
       <c r="Y306"/>
@@ -49374,11 +50137,21 @@
         <v>8</v>
       </c>
       <c r="O307" s="17"/>
-      <c r="R307"/>
-      <c r="S307"/>
-      <c r="T307"/>
-      <c r="U307"/>
-      <c r="V307"/>
+      <c r="R307" s="240">
+        <v>2</v>
+      </c>
+      <c r="S307" s="235" t="s">
+        <v>345</v>
+      </c>
+      <c r="T307" s="235" t="s">
+        <v>2856</v>
+      </c>
+      <c r="U307" s="236">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V307" s="284">
+        <v>8.75</v>
+      </c>
       <c r="W307"/>
       <c r="X307"/>
       <c r="Y307"/>
@@ -49421,11 +50194,21 @@
         <v>9</v>
       </c>
       <c r="O308" s="17"/>
-      <c r="R308"/>
-      <c r="S308"/>
-      <c r="T308"/>
-      <c r="U308"/>
-      <c r="V308"/>
+      <c r="R308" s="242">
+        <v>3</v>
+      </c>
+      <c r="S308" s="232" t="s">
+        <v>2349</v>
+      </c>
+      <c r="T308" s="232" t="s">
+        <v>2857</v>
+      </c>
+      <c r="U308" s="233">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V308" s="275">
+        <v>8.84</v>
+      </c>
       <c r="W308"/>
       <c r="X308"/>
       <c r="Y308"/>
@@ -49474,11 +50257,21 @@
         <v>9</v>
       </c>
       <c r="O309" s="17"/>
-      <c r="R309"/>
-      <c r="S309"/>
-      <c r="T309"/>
-      <c r="U309"/>
-      <c r="V309"/>
+      <c r="R309" s="244">
+        <v>4</v>
+      </c>
+      <c r="S309" s="235" t="s">
+        <v>2505</v>
+      </c>
+      <c r="T309" s="235" t="s">
+        <v>2506</v>
+      </c>
+      <c r="U309" s="236">
+        <v>7.17</v>
+      </c>
+      <c r="V309" s="249">
+        <v>7.04</v>
+      </c>
       <c r="W309"/>
       <c r="X309"/>
       <c r="Y309"/>
@@ -49530,11 +50323,21 @@
         <v>10</v>
       </c>
       <c r="O310" s="17"/>
-      <c r="R310"/>
-      <c r="S310"/>
-      <c r="T310"/>
-      <c r="U310"/>
-      <c r="V310"/>
+      <c r="R310" s="244">
+        <v>5</v>
+      </c>
+      <c r="S310" s="232" t="s">
+        <v>2639</v>
+      </c>
+      <c r="T310" s="232" t="s">
+        <v>2640</v>
+      </c>
+      <c r="U310" s="233">
+        <v>2.5</v>
+      </c>
+      <c r="V310" s="250">
+        <v>2.39</v>
+      </c>
       <c r="W310"/>
       <c r="X310"/>
       <c r="Y310"/>
@@ -49604,7 +50407,7 @@
       <c r="AH311"/>
       <c r="AI311"/>
     </row>
-    <row r="312" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>1146</v>
       </c>
@@ -49640,11 +50443,13 @@
         <v>8.5</v>
       </c>
       <c r="O312" s="17"/>
-      <c r="R312"/>
-      <c r="S312"/>
-      <c r="T312"/>
-      <c r="U312"/>
-      <c r="V312"/>
+      <c r="R312" s="359" t="s">
+        <v>2874</v>
+      </c>
+      <c r="S312" s="359"/>
+      <c r="T312" s="359"/>
+      <c r="U312" s="359"/>
+      <c r="V312" s="359"/>
       <c r="W312"/>
       <c r="X312"/>
       <c r="Y312"/>
@@ -49695,11 +50500,21 @@
         <v>8</v>
       </c>
       <c r="O313" s="17"/>
-      <c r="R313"/>
-      <c r="S313"/>
-      <c r="T313"/>
-      <c r="U313"/>
-      <c r="V313"/>
+      <c r="R313" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S313" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T313" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U313" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V313" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W313"/>
       <c r="X313"/>
       <c r="Y313"/>
@@ -49750,11 +50565,21 @@
         <v>8.5</v>
       </c>
       <c r="O314" s="17"/>
-      <c r="R314"/>
-      <c r="S314"/>
-      <c r="T314"/>
-      <c r="U314"/>
-      <c r="V314"/>
+      <c r="R314" s="238">
+        <v>1</v>
+      </c>
+      <c r="S314" s="232" t="s">
+        <v>1336</v>
+      </c>
+      <c r="T314" s="232" t="s">
+        <v>1327</v>
+      </c>
+      <c r="U314" s="233">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="V314" s="256">
+        <v>8.91</v>
+      </c>
       <c r="W314"/>
       <c r="X314"/>
       <c r="Y314"/>
@@ -49805,11 +50630,21 @@
         <v>7.5</v>
       </c>
       <c r="O315" s="17"/>
-      <c r="R315"/>
-      <c r="S315"/>
-      <c r="T315"/>
-      <c r="U315"/>
-      <c r="V315"/>
+      <c r="R315" s="240">
+        <v>2</v>
+      </c>
+      <c r="S315" s="235" t="s">
+        <v>1492</v>
+      </c>
+      <c r="T315" s="235" t="s">
+        <v>1493</v>
+      </c>
+      <c r="U315" s="236">
+        <v>8.93</v>
+      </c>
+      <c r="V315" s="258">
+        <v>8.8800000000000008</v>
+      </c>
       <c r="W315"/>
       <c r="X315"/>
       <c r="Y315"/>
@@ -49860,11 +50695,21 @@
         <v>9</v>
       </c>
       <c r="O316" s="17"/>
-      <c r="R316"/>
-      <c r="S316"/>
-      <c r="T316"/>
-      <c r="U316"/>
-      <c r="V316"/>
+      <c r="R316" s="242">
+        <v>3</v>
+      </c>
+      <c r="S316" s="232" t="s">
+        <v>339</v>
+      </c>
+      <c r="T316" s="232" t="s">
+        <v>2858</v>
+      </c>
+      <c r="U316" s="233">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="V316" s="278">
+        <v>8.4700000000000006</v>
+      </c>
       <c r="W316"/>
       <c r="X316"/>
       <c r="Y316"/>
@@ -49907,11 +50752,21 @@
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
       <c r="O317" s="17"/>
-      <c r="R317"/>
-      <c r="S317"/>
-      <c r="T317"/>
-      <c r="U317"/>
-      <c r="V317"/>
+      <c r="R317" s="244">
+        <v>4</v>
+      </c>
+      <c r="S317" s="235" t="s">
+        <v>739</v>
+      </c>
+      <c r="T317" s="235" t="s">
+        <v>740</v>
+      </c>
+      <c r="U317" s="236">
+        <v>8.86</v>
+      </c>
+      <c r="V317" s="284">
+        <v>8.75</v>
+      </c>
       <c r="W317"/>
       <c r="X317"/>
       <c r="Y317"/>
@@ -49964,11 +50819,21 @@
         <v>9.31</v>
       </c>
       <c r="O318" s="17"/>
-      <c r="R318"/>
-      <c r="S318"/>
-      <c r="T318"/>
-      <c r="U318"/>
-      <c r="V318"/>
+      <c r="R318" s="244">
+        <v>5</v>
+      </c>
+      <c r="S318" s="232" t="s">
+        <v>2410</v>
+      </c>
+      <c r="T318" s="232" t="s">
+        <v>2411</v>
+      </c>
+      <c r="U318" s="233">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="V318" s="299">
+        <v>8.1300000000000008</v>
+      </c>
       <c r="W318"/>
       <c r="X318"/>
       <c r="Y318"/>
@@ -50032,7 +50897,7 @@
       <c r="AH319"/>
       <c r="AI319"/>
     </row>
-    <row r="320" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="7" t="s">
         <v>1880</v>
       </c>
@@ -50069,11 +50934,13 @@
         <v>10.5</v>
       </c>
       <c r="O320" s="17"/>
-      <c r="R320"/>
-      <c r="S320"/>
-      <c r="T320"/>
-      <c r="U320"/>
-      <c r="V320"/>
+      <c r="R320" s="359" t="s">
+        <v>2875</v>
+      </c>
+      <c r="S320" s="359"/>
+      <c r="T320" s="359"/>
+      <c r="U320" s="359"/>
+      <c r="V320" s="359"/>
       <c r="W320"/>
       <c r="X320"/>
       <c r="Y320"/>
@@ -50120,11 +50987,21 @@
         <v>9.5</v>
       </c>
       <c r="O321" s="17"/>
-      <c r="R321"/>
-      <c r="S321"/>
-      <c r="T321"/>
-      <c r="U321"/>
-      <c r="V321"/>
+      <c r="R321" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S321" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T321" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U321" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V321" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W321"/>
       <c r="X321"/>
       <c r="Y321"/>
@@ -50176,11 +51053,21 @@
         <v>10</v>
       </c>
       <c r="O322" s="17"/>
-      <c r="R322"/>
-      <c r="S322"/>
-      <c r="T322"/>
-      <c r="U322"/>
-      <c r="V322"/>
+      <c r="R322" s="238">
+        <v>1</v>
+      </c>
+      <c r="S322" s="232" t="s">
+        <v>997</v>
+      </c>
+      <c r="T322" s="232" t="s">
+        <v>995</v>
+      </c>
+      <c r="U322" s="233">
+        <v>10.5</v>
+      </c>
+      <c r="V322" s="281">
+        <v>10.85</v>
+      </c>
       <c r="W322"/>
       <c r="X322"/>
       <c r="Y322"/>
@@ -50229,11 +51116,21 @@
         <v>9</v>
       </c>
       <c r="O323" s="17"/>
-      <c r="R323"/>
-      <c r="S323"/>
-      <c r="T323"/>
-      <c r="U323"/>
-      <c r="V323"/>
+      <c r="R323" s="240">
+        <v>2</v>
+      </c>
+      <c r="S323" s="235" t="s">
+        <v>346</v>
+      </c>
+      <c r="T323" s="235" t="s">
+        <v>2859</v>
+      </c>
+      <c r="U323" s="236">
+        <v>8.85</v>
+      </c>
+      <c r="V323" s="275">
+        <v>8.84</v>
+      </c>
       <c r="W323"/>
       <c r="X323"/>
       <c r="Y323"/>
@@ -50284,11 +51181,21 @@
         <v>8.5</v>
       </c>
       <c r="O324" s="17"/>
-      <c r="R324"/>
-      <c r="S324"/>
-      <c r="T324"/>
-      <c r="U324"/>
-      <c r="V324"/>
+      <c r="R324" s="242">
+        <v>3</v>
+      </c>
+      <c r="S324" s="232" t="s">
+        <v>1492</v>
+      </c>
+      <c r="T324" s="232" t="s">
+        <v>1493</v>
+      </c>
+      <c r="U324" s="233">
+        <v>8.93</v>
+      </c>
+      <c r="V324" s="258">
+        <v>8.8800000000000008</v>
+      </c>
       <c r="W324"/>
       <c r="X324"/>
       <c r="Y324"/>
@@ -50339,11 +51246,21 @@
         <v>8.5</v>
       </c>
       <c r="O325" s="17"/>
-      <c r="R325"/>
-      <c r="S325"/>
-      <c r="T325"/>
-      <c r="U325"/>
-      <c r="V325"/>
+      <c r="R325" s="244">
+        <v>4</v>
+      </c>
+      <c r="S325" s="235" t="s">
+        <v>396</v>
+      </c>
+      <c r="T325" s="235" t="s">
+        <v>390</v>
+      </c>
+      <c r="U325" s="236">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V325" s="261">
+        <v>8.81</v>
+      </c>
       <c r="W325"/>
       <c r="X325"/>
       <c r="Y325"/>
@@ -50394,11 +51311,21 @@
         <v>8.5</v>
       </c>
       <c r="O326" s="17"/>
-      <c r="R326"/>
-      <c r="S326"/>
-      <c r="T326"/>
-      <c r="U326"/>
-      <c r="V326"/>
+      <c r="R326" s="244">
+        <v>5</v>
+      </c>
+      <c r="S326" s="232" t="s">
+        <v>957</v>
+      </c>
+      <c r="T326" s="232" t="s">
+        <v>955</v>
+      </c>
+      <c r="U326" s="233">
+        <v>8.67</v>
+      </c>
+      <c r="V326" s="264">
+        <v>8.56</v>
+      </c>
       <c r="W326"/>
       <c r="X326"/>
       <c r="Y326"/>
@@ -50456,7 +51383,7 @@
       <c r="AH327"/>
       <c r="AI327"/>
     </row>
-    <row r="328" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>2047</v>
       </c>
@@ -50491,11 +51418,13 @@
         <v>8.81</v>
       </c>
       <c r="O328" s="17"/>
-      <c r="R328"/>
-      <c r="S328"/>
-      <c r="T328"/>
-      <c r="U328"/>
-      <c r="V328"/>
+      <c r="R328" s="359" t="s">
+        <v>2876</v>
+      </c>
+      <c r="S328" s="359"/>
+      <c r="T328" s="359"/>
+      <c r="U328" s="359"/>
+      <c r="V328" s="359"/>
       <c r="W328"/>
       <c r="X328"/>
       <c r="Y328"/>
@@ -50547,11 +51476,21 @@
         <v>9</v>
       </c>
       <c r="O329" s="17"/>
-      <c r="R329"/>
-      <c r="S329"/>
-      <c r="T329"/>
-      <c r="U329"/>
-      <c r="V329"/>
+      <c r="R329" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S329" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T329" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U329" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V329" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W329"/>
       <c r="X329"/>
       <c r="Y329"/>
@@ -50600,11 +51539,21 @@
         <v>8.5</v>
       </c>
       <c r="O330" s="17"/>
-      <c r="R330"/>
-      <c r="S330"/>
-      <c r="T330"/>
-      <c r="U330"/>
-      <c r="V330"/>
+      <c r="R330" s="238">
+        <v>1</v>
+      </c>
+      <c r="S330" s="232" t="s">
+        <v>326</v>
+      </c>
+      <c r="T330" s="232" t="s">
+        <v>2860</v>
+      </c>
+      <c r="U330" s="233">
+        <v>9.34</v>
+      </c>
+      <c r="V330" s="367">
+        <v>9.64</v>
+      </c>
       <c r="W330"/>
       <c r="X330"/>
       <c r="Y330"/>
@@ -50655,11 +51604,21 @@
         <v>9.5</v>
       </c>
       <c r="O331" s="17"/>
-      <c r="R331"/>
-      <c r="S331"/>
-      <c r="T331"/>
-      <c r="U331"/>
-      <c r="V331"/>
+      <c r="R331" s="240">
+        <v>2</v>
+      </c>
+      <c r="S331" s="235" t="s">
+        <v>1412</v>
+      </c>
+      <c r="T331" s="235" t="s">
+        <v>1413</v>
+      </c>
+      <c r="U331" s="236">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="V331" s="268">
+        <v>7.95</v>
+      </c>
       <c r="W331"/>
       <c r="X331"/>
       <c r="Y331"/>
@@ -50710,11 +51669,21 @@
         <v>10.5</v>
       </c>
       <c r="O332" s="17"/>
-      <c r="R332"/>
-      <c r="S332"/>
-      <c r="T332"/>
-      <c r="U332"/>
-      <c r="V332"/>
+      <c r="R332" s="242">
+        <v>3</v>
+      </c>
+      <c r="S332" s="232" t="s">
+        <v>335</v>
+      </c>
+      <c r="T332" s="232" t="s">
+        <v>1793</v>
+      </c>
+      <c r="U332" s="233">
+        <v>3.68</v>
+      </c>
+      <c r="V332" s="250">
+        <v>3.37</v>
+      </c>
       <c r="W332"/>
       <c r="X332"/>
       <c r="Y332"/>
@@ -50894,7 +51863,7 @@
       <c r="AH335"/>
       <c r="AI335"/>
     </row>
-    <row r="336" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>2055</v>
       </c>
@@ -50930,11 +51899,13 @@
         <v>8</v>
       </c>
       <c r="O336" s="17"/>
-      <c r="R336"/>
-      <c r="S336"/>
-      <c r="T336"/>
-      <c r="U336"/>
-      <c r="V336"/>
+      <c r="R336" s="359" t="s">
+        <v>2877</v>
+      </c>
+      <c r="S336" s="359"/>
+      <c r="T336" s="359"/>
+      <c r="U336" s="359"/>
+      <c r="V336" s="359"/>
       <c r="W336"/>
       <c r="X336"/>
       <c r="Y336"/>
@@ -50981,11 +51952,21 @@
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
       <c r="O337" s="17"/>
-      <c r="R337"/>
-      <c r="S337"/>
-      <c r="T337"/>
-      <c r="U337"/>
-      <c r="V337"/>
+      <c r="R337" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S337" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T337" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U337" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V337" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W337"/>
       <c r="X337"/>
       <c r="Y337"/>
@@ -51033,11 +52014,21 @@
         <v>8.73</v>
       </c>
       <c r="O338" s="17"/>
-      <c r="R338"/>
-      <c r="S338"/>
-      <c r="T338"/>
-      <c r="U338"/>
-      <c r="V338"/>
+      <c r="R338" s="238">
+        <v>1</v>
+      </c>
+      <c r="S338" s="232" t="s">
+        <v>2702</v>
+      </c>
+      <c r="T338" s="232" t="s">
+        <v>2861</v>
+      </c>
+      <c r="U338" s="233">
+        <v>9.36</v>
+      </c>
+      <c r="V338" s="300">
+        <v>9.5299999999999994</v>
+      </c>
       <c r="W338"/>
       <c r="X338"/>
       <c r="Y338"/>
@@ -51085,11 +52076,21 @@
         <v>8</v>
       </c>
       <c r="O339" s="17"/>
-      <c r="R339"/>
-      <c r="S339"/>
-      <c r="T339"/>
-      <c r="U339"/>
-      <c r="V339"/>
+      <c r="R339" s="240">
+        <v>2</v>
+      </c>
+      <c r="S339" s="235" t="s">
+        <v>2725</v>
+      </c>
+      <c r="T339" s="235" t="s">
+        <v>2724</v>
+      </c>
+      <c r="U339" s="236">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="V339" s="261">
+        <v>8.81</v>
+      </c>
       <c r="W339"/>
       <c r="X339"/>
       <c r="Y339"/>
@@ -51141,11 +52142,21 @@
         <v>9</v>
       </c>
       <c r="O340" s="17"/>
-      <c r="R340"/>
-      <c r="S340"/>
-      <c r="T340"/>
-      <c r="U340"/>
-      <c r="V340"/>
+      <c r="R340" s="242">
+        <v>3</v>
+      </c>
+      <c r="S340" s="232" t="s">
+        <v>1675</v>
+      </c>
+      <c r="T340" s="232" t="s">
+        <v>1674</v>
+      </c>
+      <c r="U340" s="233">
+        <v>8.85</v>
+      </c>
+      <c r="V340" s="313">
+        <v>8.7799999999999994</v>
+      </c>
       <c r="W340"/>
       <c r="X340"/>
       <c r="Y340"/>
@@ -51194,11 +52205,21 @@
       </c>
       <c r="N341" s="151"/>
       <c r="O341" s="17"/>
-      <c r="R341"/>
-      <c r="S341"/>
-      <c r="T341"/>
-      <c r="U341"/>
-      <c r="V341"/>
+      <c r="R341" s="244">
+        <v>4</v>
+      </c>
+      <c r="S341" s="235" t="s">
+        <v>1779</v>
+      </c>
+      <c r="T341" s="235" t="s">
+        <v>1780</v>
+      </c>
+      <c r="U341" s="236">
+        <v>8.83</v>
+      </c>
+      <c r="V341" s="289">
+        <v>8.77</v>
+      </c>
       <c r="W341"/>
       <c r="X341"/>
       <c r="Y341"/>
@@ -51245,11 +52266,21 @@
         <v>10</v>
       </c>
       <c r="O342" s="17"/>
-      <c r="R342"/>
-      <c r="S342"/>
-      <c r="T342"/>
-      <c r="U342"/>
-      <c r="V342"/>
+      <c r="R342" s="244">
+        <v>5</v>
+      </c>
+      <c r="S342" s="232" t="s">
+        <v>957</v>
+      </c>
+      <c r="T342" s="232" t="s">
+        <v>955</v>
+      </c>
+      <c r="U342" s="233">
+        <v>8.67</v>
+      </c>
+      <c r="V342" s="264">
+        <v>8.56</v>
+      </c>
       <c r="W342"/>
       <c r="X342"/>
       <c r="Y342"/>
@@ -51320,7 +52351,7 @@
       <c r="AH343"/>
       <c r="AI343"/>
     </row>
-    <row r="344" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="11" t="s">
         <v>2273</v>
       </c>
@@ -51356,11 +52387,13 @@
         <v>8.5</v>
       </c>
       <c r="O344" s="17"/>
-      <c r="R344"/>
-      <c r="S344"/>
-      <c r="T344"/>
-      <c r="U344"/>
-      <c r="V344"/>
+      <c r="R344" s="359" t="s">
+        <v>2878</v>
+      </c>
+      <c r="S344" s="359"/>
+      <c r="T344" s="359"/>
+      <c r="U344" s="359"/>
+      <c r="V344" s="359"/>
       <c r="W344"/>
       <c r="X344"/>
       <c r="Y344"/>
@@ -51411,11 +52444,21 @@
         <v>8.5</v>
       </c>
       <c r="O345" s="17"/>
-      <c r="R345"/>
-      <c r="S345"/>
-      <c r="T345"/>
-      <c r="U345"/>
-      <c r="V345"/>
+      <c r="R345" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S345" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T345" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U345" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V345" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W345"/>
       <c r="X345"/>
       <c r="Y345"/>
@@ -51466,11 +52509,21 @@
         <v>9</v>
       </c>
       <c r="O346" s="17"/>
-      <c r="R346"/>
-      <c r="S346"/>
-      <c r="T346"/>
-      <c r="U346"/>
-      <c r="V346"/>
+      <c r="R346" s="238">
+        <v>1</v>
+      </c>
+      <c r="S346" s="232" t="s">
+        <v>336</v>
+      </c>
+      <c r="T346" s="232" t="s">
+        <v>188</v>
+      </c>
+      <c r="U346" s="233">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="V346" s="287">
+        <v>9.34</v>
+      </c>
       <c r="W346"/>
       <c r="X346"/>
       <c r="Y346"/>
@@ -51521,11 +52574,21 @@
         <v>8.5</v>
       </c>
       <c r="O347" s="17"/>
-      <c r="R347"/>
-      <c r="S347"/>
-      <c r="T347"/>
-      <c r="U347"/>
-      <c r="V347"/>
+      <c r="R347" s="240">
+        <v>2</v>
+      </c>
+      <c r="S347" s="235" t="s">
+        <v>396</v>
+      </c>
+      <c r="T347" s="235" t="s">
+        <v>390</v>
+      </c>
+      <c r="U347" s="236">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V347" s="261">
+        <v>8.81</v>
+      </c>
       <c r="W347"/>
       <c r="X347"/>
       <c r="Y347"/>
@@ -51576,11 +52639,21 @@
         <v>8</v>
       </c>
       <c r="O348" s="17"/>
-      <c r="R348"/>
-      <c r="S348"/>
-      <c r="T348"/>
-      <c r="U348"/>
-      <c r="V348"/>
+      <c r="R348" s="242">
+        <v>3</v>
+      </c>
+      <c r="S348" s="232" t="s">
+        <v>2637</v>
+      </c>
+      <c r="T348" s="232" t="s">
+        <v>2638</v>
+      </c>
+      <c r="U348" s="233">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="V348" s="289">
+        <v>8.77</v>
+      </c>
       <c r="W348"/>
       <c r="X348"/>
       <c r="Y348"/>
@@ -51629,11 +52702,21 @@
       </c>
       <c r="N349" s="151"/>
       <c r="O349" s="17"/>
-      <c r="R349"/>
-      <c r="S349"/>
-      <c r="T349"/>
-      <c r="U349"/>
-      <c r="V349"/>
+      <c r="R349" s="244">
+        <v>4</v>
+      </c>
+      <c r="S349" s="235" t="s">
+        <v>2758</v>
+      </c>
+      <c r="T349" s="235" t="s">
+        <v>2759</v>
+      </c>
+      <c r="U349" s="236">
+        <v>8.75</v>
+      </c>
+      <c r="V349" s="248">
+        <v>8.67</v>
+      </c>
       <c r="W349"/>
       <c r="X349"/>
       <c r="Y349"/>
@@ -51684,11 +52767,21 @@
         <v>9</v>
       </c>
       <c r="O350" s="17"/>
-      <c r="R350"/>
-      <c r="S350"/>
-      <c r="T350"/>
-      <c r="U350"/>
-      <c r="V350"/>
+      <c r="R350" s="244">
+        <v>5</v>
+      </c>
+      <c r="S350" s="232" t="s">
+        <v>1635</v>
+      </c>
+      <c r="T350" s="232" t="s">
+        <v>1636</v>
+      </c>
+      <c r="U350" s="233">
+        <v>8.6</v>
+      </c>
+      <c r="V350" s="326">
+        <v>8.5</v>
+      </c>
       <c r="W350"/>
       <c r="X350"/>
       <c r="Y350"/>
@@ -51758,7 +52851,7 @@
       <c r="AH351"/>
       <c r="AI351"/>
     </row>
-    <row r="352" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>2281</v>
       </c>
@@ -51790,11 +52883,13 @@
         <v>8</v>
       </c>
       <c r="O352" s="17"/>
-      <c r="R352"/>
-      <c r="S352"/>
-      <c r="T352"/>
-      <c r="U352"/>
-      <c r="V352"/>
+      <c r="R352" s="359" t="s">
+        <v>2879</v>
+      </c>
+      <c r="S352" s="359"/>
+      <c r="T352" s="359"/>
+      <c r="U352" s="359"/>
+      <c r="V352" s="359"/>
       <c r="W352"/>
       <c r="X352"/>
       <c r="Y352"/>
@@ -51844,11 +52939,21 @@
         <v>9</v>
       </c>
       <c r="O353" s="17"/>
-      <c r="R353"/>
-      <c r="S353"/>
-      <c r="T353"/>
-      <c r="U353"/>
-      <c r="V353"/>
+      <c r="R353" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S353" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T353" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U353" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V353" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W353"/>
       <c r="X353"/>
       <c r="Y353"/>
@@ -51895,11 +53000,21 @@
       <c r="M354" s="2"/>
       <c r="N354" s="2"/>
       <c r="O354" s="17"/>
-      <c r="R354"/>
-      <c r="S354"/>
-      <c r="T354"/>
-      <c r="U354"/>
-      <c r="V354"/>
+      <c r="R354" s="238">
+        <v>1</v>
+      </c>
+      <c r="S354" s="232" t="s">
+        <v>326</v>
+      </c>
+      <c r="T354" s="232" t="s">
+        <v>1246</v>
+      </c>
+      <c r="U354" s="233">
+        <v>9.36</v>
+      </c>
+      <c r="V354" s="335">
+        <v>9.73</v>
+      </c>
       <c r="W354"/>
       <c r="X354"/>
       <c r="Y354"/>
@@ -51947,11 +53062,21 @@
         <v>8</v>
       </c>
       <c r="O355" s="17"/>
-      <c r="R355"/>
-      <c r="S355"/>
-      <c r="T355"/>
-      <c r="U355"/>
-      <c r="V355"/>
+      <c r="R355" s="240">
+        <v>2</v>
+      </c>
+      <c r="S355" s="235" t="s">
+        <v>1442</v>
+      </c>
+      <c r="T355" s="235" t="s">
+        <v>2862</v>
+      </c>
+      <c r="U355" s="236">
+        <v>8.77</v>
+      </c>
+      <c r="V355" s="248">
+        <v>8.67</v>
+      </c>
       <c r="W355"/>
       <c r="X355"/>
       <c r="Y355"/>
@@ -52003,11 +53128,21 @@
         <v>9</v>
       </c>
       <c r="O356" s="17"/>
-      <c r="R356"/>
-      <c r="S356"/>
-      <c r="T356"/>
-      <c r="U356"/>
-      <c r="V356"/>
+      <c r="R356" s="242">
+        <v>3</v>
+      </c>
+      <c r="S356" s="232" t="s">
+        <v>1241</v>
+      </c>
+      <c r="T356" s="232" t="s">
+        <v>1236</v>
+      </c>
+      <c r="U356" s="233">
+        <v>8.75</v>
+      </c>
+      <c r="V356" s="271">
+        <v>8.6300000000000008</v>
+      </c>
       <c r="W356"/>
       <c r="X356"/>
       <c r="Y356"/>
@@ -52058,11 +53193,21 @@
         <v>8.5</v>
       </c>
       <c r="O357" s="17"/>
-      <c r="R357"/>
-      <c r="S357"/>
-      <c r="T357"/>
-      <c r="U357"/>
-      <c r="V357"/>
+      <c r="R357" s="244">
+        <v>4</v>
+      </c>
+      <c r="S357" s="235" t="s">
+        <v>2363</v>
+      </c>
+      <c r="T357" s="235" t="s">
+        <v>2362</v>
+      </c>
+      <c r="U357" s="236">
+        <v>8.61</v>
+      </c>
+      <c r="V357" s="252">
+        <v>8.52</v>
+      </c>
       <c r="W357"/>
       <c r="X357"/>
       <c r="Y357"/>
@@ -52113,11 +53258,21 @@
         <v>8</v>
       </c>
       <c r="O358" s="17"/>
-      <c r="R358"/>
-      <c r="S358"/>
-      <c r="T358"/>
-      <c r="U358"/>
-      <c r="V358"/>
+      <c r="R358" s="244">
+        <v>5</v>
+      </c>
+      <c r="S358" s="232" t="s">
+        <v>1660</v>
+      </c>
+      <c r="T358" s="232" t="s">
+        <v>1661</v>
+      </c>
+      <c r="U358" s="233">
+        <v>8.4</v>
+      </c>
+      <c r="V358" s="309">
+        <v>8.3699999999999992</v>
+      </c>
       <c r="W358"/>
       <c r="X358"/>
       <c r="Y358"/>
@@ -52179,7 +53334,7 @@
       <c r="AH359"/>
       <c r="AI359"/>
     </row>
-    <row r="360" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="188" t="s">
         <v>2332</v>
       </c>
@@ -52217,11 +53372,13 @@
         <v>7.5</v>
       </c>
       <c r="O360" s="17"/>
-      <c r="R360"/>
-      <c r="S360"/>
-      <c r="T360"/>
-      <c r="U360"/>
-      <c r="V360"/>
+      <c r="R360" s="359" t="s">
+        <v>2880</v>
+      </c>
+      <c r="S360" s="359"/>
+      <c r="T360" s="359"/>
+      <c r="U360" s="359"/>
+      <c r="V360" s="359"/>
       <c r="W360"/>
       <c r="X360"/>
       <c r="Y360"/>
@@ -52272,11 +53429,21 @@
         <v>8</v>
       </c>
       <c r="O361" s="17"/>
-      <c r="R361"/>
-      <c r="S361"/>
-      <c r="T361"/>
-      <c r="U361"/>
-      <c r="V361"/>
+      <c r="R361" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S361" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T361" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U361" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V361" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W361"/>
       <c r="X361"/>
       <c r="Y361"/>
@@ -52327,11 +53494,21 @@
         <v>8</v>
       </c>
       <c r="O362" s="17"/>
-      <c r="R362"/>
-      <c r="S362"/>
-      <c r="T362"/>
-      <c r="U362"/>
-      <c r="V362"/>
+      <c r="R362" s="238">
+        <v>1</v>
+      </c>
+      <c r="S362" s="232" t="s">
+        <v>335</v>
+      </c>
+      <c r="T362" s="232" t="s">
+        <v>2863</v>
+      </c>
+      <c r="U362" s="233">
+        <v>9.02</v>
+      </c>
+      <c r="V362" s="362">
+        <v>9.07</v>
+      </c>
       <c r="W362"/>
       <c r="X362"/>
       <c r="Y362"/>
@@ -52382,11 +53559,21 @@
         <v>8</v>
       </c>
       <c r="O363" s="17"/>
-      <c r="R363"/>
-      <c r="S363"/>
-      <c r="T363"/>
-      <c r="U363"/>
-      <c r="V363"/>
+      <c r="R363" s="240">
+        <v>2</v>
+      </c>
+      <c r="S363" s="235" t="s">
+        <v>338</v>
+      </c>
+      <c r="T363" s="235" t="s">
+        <v>2864</v>
+      </c>
+      <c r="U363" s="236">
+        <v>8.39</v>
+      </c>
+      <c r="V363" s="309">
+        <v>8.3699999999999992</v>
+      </c>
       <c r="W363"/>
       <c r="X363"/>
       <c r="Y363"/>
@@ -52610,7 +53797,7 @@
       <c r="AH367"/>
       <c r="AI367"/>
     </row>
-    <row r="368" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>2340</v>
       </c>
@@ -52646,11 +53833,13 @@
         <v>8.5</v>
       </c>
       <c r="O368" s="17"/>
-      <c r="R368"/>
-      <c r="S368"/>
-      <c r="T368"/>
-      <c r="U368"/>
-      <c r="V368"/>
+      <c r="R368" s="359" t="s">
+        <v>2881</v>
+      </c>
+      <c r="S368" s="359"/>
+      <c r="T368" s="359"/>
+      <c r="U368" s="359"/>
+      <c r="V368" s="359"/>
       <c r="W368"/>
       <c r="X368"/>
       <c r="Y368"/>
@@ -52699,11 +53888,21 @@
         <v>8</v>
       </c>
       <c r="O369" s="17"/>
-      <c r="R369"/>
-      <c r="S369"/>
-      <c r="T369"/>
-      <c r="U369"/>
-      <c r="V369"/>
+      <c r="R369" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S369" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T369" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U369" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V369" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W369"/>
       <c r="X369"/>
       <c r="Y369"/>
@@ -52754,11 +53953,21 @@
         <v>8</v>
       </c>
       <c r="O370" s="17"/>
-      <c r="R370"/>
-      <c r="S370"/>
-      <c r="T370"/>
-      <c r="U370"/>
-      <c r="V370"/>
+      <c r="R370" s="238">
+        <v>1</v>
+      </c>
+      <c r="S370" s="232" t="s">
+        <v>327</v>
+      </c>
+      <c r="T370" s="232" t="s">
+        <v>2865</v>
+      </c>
+      <c r="U370" s="233">
+        <v>8.52</v>
+      </c>
+      <c r="V370" s="264">
+        <v>8.56</v>
+      </c>
       <c r="W370"/>
       <c r="X370"/>
       <c r="Y370"/>
@@ -52805,11 +54014,21 @@
         <v>8</v>
       </c>
       <c r="O371" s="17"/>
-      <c r="R371"/>
-      <c r="S371"/>
-      <c r="T371"/>
-      <c r="U371"/>
-      <c r="V371"/>
+      <c r="R371" s="240">
+        <v>2</v>
+      </c>
+      <c r="S371" s="235" t="s">
+        <v>337</v>
+      </c>
+      <c r="T371" s="235" t="s">
+        <v>2866</v>
+      </c>
+      <c r="U371" s="236">
+        <v>8.61</v>
+      </c>
+      <c r="V371" s="308">
+        <v>8.61</v>
+      </c>
       <c r="W371"/>
       <c r="X371"/>
       <c r="Y371"/>
@@ -53039,7 +54258,7 @@
       <c r="AH375"/>
       <c r="AI375"/>
     </row>
-    <row r="376" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>2084</v>
       </c>
@@ -53075,11 +54294,13 @@
         <v>10</v>
       </c>
       <c r="O376" s="17"/>
-      <c r="R376"/>
-      <c r="S376"/>
-      <c r="T376"/>
-      <c r="U376"/>
-      <c r="V376"/>
+      <c r="R376" s="359" t="s">
+        <v>2882</v>
+      </c>
+      <c r="S376" s="359"/>
+      <c r="T376" s="359"/>
+      <c r="U376" s="359"/>
+      <c r="V376" s="359"/>
       <c r="W376"/>
       <c r="X376"/>
       <c r="Y376"/>
@@ -53128,11 +54349,21 @@
         <v>8</v>
       </c>
       <c r="O377" s="17"/>
-      <c r="R377"/>
-      <c r="S377"/>
-      <c r="T377"/>
-      <c r="U377"/>
-      <c r="V377"/>
+      <c r="R377" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="S377" s="231" t="s">
+        <v>319</v>
+      </c>
+      <c r="T377" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="U377" s="231" t="s">
+        <v>321</v>
+      </c>
+      <c r="V377" s="231" t="s">
+        <v>1003</v>
+      </c>
       <c r="W377"/>
       <c r="X377"/>
       <c r="Y377"/>
@@ -53179,11 +54410,21 @@
         <v>9.5</v>
       </c>
       <c r="O378" s="17"/>
-      <c r="R378"/>
-      <c r="S378"/>
-      <c r="T378"/>
-      <c r="U378"/>
-      <c r="V378"/>
+      <c r="R378" s="238">
+        <v>1</v>
+      </c>
+      <c r="S378" s="232" t="s">
+        <v>1376</v>
+      </c>
+      <c r="T378" s="232" t="s">
+        <v>1377</v>
+      </c>
+      <c r="U378" s="233">
+        <v>8.82</v>
+      </c>
+      <c r="V378" s="258">
+        <v>8.8800000000000008</v>
+      </c>
       <c r="W378"/>
       <c r="X378"/>
       <c r="Y378"/>
@@ -53231,11 +54472,21 @@
         <v>8</v>
       </c>
       <c r="O379" s="17"/>
-      <c r="R379"/>
-      <c r="S379"/>
-      <c r="T379"/>
-      <c r="U379"/>
-      <c r="V379"/>
+      <c r="R379" s="240">
+        <v>2</v>
+      </c>
+      <c r="S379" s="235" t="s">
+        <v>838</v>
+      </c>
+      <c r="T379" s="235" t="s">
+        <v>2867</v>
+      </c>
+      <c r="U379" s="236">
+        <v>8.64</v>
+      </c>
+      <c r="V379" s="271">
+        <v>8.6300000000000008</v>
+      </c>
       <c r="W379"/>
       <c r="X379"/>
       <c r="Y379"/>
@@ -53287,11 +54538,21 @@
         <v>8</v>
       </c>
       <c r="O380" s="17"/>
-      <c r="R380"/>
-      <c r="S380"/>
-      <c r="T380"/>
-      <c r="U380"/>
-      <c r="V380"/>
+      <c r="R380" s="242">
+        <v>3</v>
+      </c>
+      <c r="S380" s="232" t="s">
+        <v>1461</v>
+      </c>
+      <c r="T380" s="232" t="s">
+        <v>1466</v>
+      </c>
+      <c r="U380" s="233">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V380" s="292">
+        <v>8.68</v>
+      </c>
       <c r="W380"/>
       <c r="X380"/>
       <c r="Y380"/>
@@ -53342,11 +54603,21 @@
         <v>8</v>
       </c>
       <c r="O381" s="17"/>
-      <c r="R381"/>
-      <c r="S381"/>
-      <c r="T381"/>
-      <c r="U381"/>
-      <c r="V381"/>
+      <c r="R381" s="244">
+        <v>4</v>
+      </c>
+      <c r="S381" s="235" t="s">
+        <v>2267</v>
+      </c>
+      <c r="T381" s="235" t="s">
+        <v>2268</v>
+      </c>
+      <c r="U381" s="236">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="V381" s="239">
+        <v>8.41</v>
+      </c>
       <c r="W381"/>
       <c r="X381"/>
       <c r="Y381"/>
@@ -56912,8 +58183,24 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S197:W216">
     <sortCondition ref="W197:W216"/>
   </sortState>
-  <mergeCells count="4">
+  <mergeCells count="20">
+    <mergeCell ref="R272:V272"/>
+    <mergeCell ref="R280:V280"/>
+    <mergeCell ref="R288:V288"/>
+    <mergeCell ref="R296:V296"/>
+    <mergeCell ref="R312:V312"/>
+    <mergeCell ref="R320:V320"/>
+    <mergeCell ref="R328:V328"/>
+    <mergeCell ref="R344:V344"/>
+    <mergeCell ref="R352:V352"/>
+    <mergeCell ref="R360:V360"/>
+    <mergeCell ref="R368:V368"/>
+    <mergeCell ref="R376:V376"/>
+    <mergeCell ref="R336:V336"/>
+    <mergeCell ref="R304:V304"/>
     <mergeCell ref="R205:V205"/>
+    <mergeCell ref="R233:V233"/>
+    <mergeCell ref="R264:V264"/>
     <mergeCell ref="R1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="R175:AE175"/>

--- a/1000albums.xlsx
+++ b/1000albums.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrodriguez\Desktop\top1000albums\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC3AE4F-29AE-4A2D-B8BB-5706261187C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7229A3D7-DA3E-4E8D-B10B-09F82F0D217F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="-15300" windowWidth="25905" windowHeight="13530" activeTab="3" xr2:uid="{0EA344FB-F653-8A4E-9162-CD1E4229299E}"/>
+    <workbookView xWindow="990" yWindow="-15300" windowWidth="25905" windowHeight="11775" xr2:uid="{0EA344FB-F653-8A4E-9162-CD1E4229299E}"/>
   </bookViews>
   <sheets>
     <sheet name="Albums" sheetId="4" r:id="rId1"/>
@@ -16601,7 +16601,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF642222"/>
+        <fgColor rgb="FF954209"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -17937,11 +17937,11 @@
     <xf numFmtId="0" fontId="116" fillId="69" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="294" fillId="271" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28207,6 +28207,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF954209"/>
+      <color rgb="FF93550B"/>
       <color rgb="FFE4C52C"/>
       <color rgb="FFF3ED05"/>
       <color rgb="FF642222"/>
@@ -28215,8 +28217,6 @@
       <color rgb="FFFCFC9E"/>
       <color rgb="FFC8C364"/>
       <color rgb="FF365264"/>
-      <color rgb="FF9A8C36"/>
-      <color rgb="FF8B7E31"/>
     </mruColors>
   </colors>
   <extLst>
@@ -56332,7 +56332,7 @@
       <c r="G499" s="2"/>
       <c r="H499" s="2"/>
       <c r="I499" s="2"/>
-      <c r="J499" s="386" t="s">
+      <c r="J499" s="388" t="s">
         <v>3233</v>
       </c>
       <c r="K499" s="12">
@@ -80956,10 +80956,10 @@
       <c r="A3" s="251">
         <v>1</v>
       </c>
-      <c r="B3" s="388" t="s">
+      <c r="B3" s="387" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="388" t="s">
+      <c r="C3" s="387" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="245" t="s">
@@ -80973,10 +80973,10 @@
       <c r="A4" s="253">
         <v>2</v>
       </c>
-      <c r="B4" s="387" t="s">
+      <c r="B4" s="386" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="387" t="s">
+      <c r="C4" s="386" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="248" t="s">
@@ -80990,10 +80990,10 @@
       <c r="A5" s="254">
         <v>3</v>
       </c>
-      <c r="B5" s="388" t="s">
+      <c r="B5" s="387" t="s">
         <v>969</v>
       </c>
-      <c r="C5" s="388" t="s">
+      <c r="C5" s="387" t="s">
         <v>969</v>
       </c>
       <c r="D5" s="245" t="s">
@@ -81007,10 +81007,10 @@
       <c r="A6" s="255">
         <v>4</v>
       </c>
-      <c r="B6" s="387" t="s">
+      <c r="B6" s="386" t="s">
         <v>999</v>
       </c>
-      <c r="C6" s="387" t="s">
+      <c r="C6" s="386" t="s">
         <v>1002</v>
       </c>
       <c r="D6" s="248" t="s">
@@ -81024,10 +81024,10 @@
       <c r="A7" s="255">
         <v>5</v>
       </c>
-      <c r="B7" s="388" t="s">
+      <c r="B7" s="387" t="s">
         <v>1002</v>
       </c>
-      <c r="C7" s="388" t="s">
+      <c r="C7" s="387" t="s">
         <v>1002</v>
       </c>
       <c r="D7" s="245" t="s">
@@ -81041,10 +81041,10 @@
       <c r="A8" s="255">
         <v>6</v>
       </c>
-      <c r="B8" s="387" t="s">
+      <c r="B8" s="386" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="387" t="s">
+      <c r="C8" s="386" t="s">
         <v>303</v>
       </c>
       <c r="D8" s="248" t="s">
@@ -81058,10 +81058,10 @@
       <c r="A9" s="255">
         <v>7</v>
       </c>
-      <c r="B9" s="388" t="s">
+      <c r="B9" s="387" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="388" t="s">
+      <c r="C9" s="387" t="s">
         <v>303</v>
       </c>
       <c r="D9" s="245" t="s">
@@ -81075,10 +81075,10 @@
       <c r="A10" s="255">
         <v>8</v>
       </c>
-      <c r="B10" s="387" t="s">
+      <c r="B10" s="386" t="s">
         <v>645</v>
       </c>
-      <c r="C10" s="387" t="s">
+      <c r="C10" s="386" t="s">
         <v>649</v>
       </c>
       <c r="D10" s="248" t="s">
@@ -81092,10 +81092,10 @@
       <c r="A11" s="255">
         <v>9</v>
       </c>
-      <c r="B11" s="388" t="s">
+      <c r="B11" s="387" t="s">
         <v>647</v>
       </c>
-      <c r="C11" s="388" t="s">
+      <c r="C11" s="387" t="s">
         <v>649</v>
       </c>
       <c r="D11" s="245" t="s">
@@ -81109,10 +81109,10 @@
       <c r="A12" s="255">
         <v>10</v>
       </c>
-      <c r="B12" s="387" t="s">
+      <c r="B12" s="386" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="387" t="s">
+      <c r="C12" s="386" t="s">
         <v>304</v>
       </c>
       <c r="D12" s="248" t="s">
@@ -81126,10 +81126,10 @@
       <c r="A13" s="255">
         <v>11</v>
       </c>
-      <c r="B13" s="388" t="s">
+      <c r="B13" s="387" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="388" t="s">
+      <c r="C13" s="387" t="s">
         <v>304</v>
       </c>
       <c r="D13" s="245" t="s">
@@ -81143,10 +81143,10 @@
       <c r="A14" s="255">
         <v>12</v>
       </c>
-      <c r="B14" s="387" t="s">
+      <c r="B14" s="386" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="387" t="s">
+      <c r="C14" s="386" t="s">
         <v>308</v>
       </c>
       <c r="D14" s="248" t="s">
@@ -81160,10 +81160,10 @@
       <c r="A15" s="255">
         <v>13</v>
       </c>
-      <c r="B15" s="388" t="s">
+      <c r="B15" s="387" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="388" t="s">
+      <c r="C15" s="387" t="s">
         <v>308</v>
       </c>
       <c r="D15" s="245" t="s">
@@ -81177,10 +81177,10 @@
       <c r="A16" s="255">
         <v>14</v>
       </c>
-      <c r="B16" s="387" t="s">
+      <c r="B16" s="386" t="s">
         <v>521</v>
       </c>
-      <c r="C16" s="387" t="s">
+      <c r="C16" s="386" t="s">
         <v>532</v>
       </c>
       <c r="D16" s="248" t="s">
@@ -81194,10 +81194,10 @@
       <c r="A17" s="255">
         <v>15</v>
       </c>
-      <c r="B17" s="388" t="s">
+      <c r="B17" s="387" t="s">
         <v>528</v>
       </c>
-      <c r="C17" s="388" t="s">
+      <c r="C17" s="387" t="s">
         <v>532</v>
       </c>
       <c r="D17" s="245" t="s">
@@ -81211,10 +81211,10 @@
       <c r="A18" s="255">
         <v>16</v>
       </c>
-      <c r="B18" s="387" t="s">
+      <c r="B18" s="386" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="387" t="s">
+      <c r="C18" s="386" t="s">
         <v>156</v>
       </c>
       <c r="D18" s="248" t="s">
@@ -81228,10 +81228,10 @@
       <c r="A19" s="255">
         <v>17</v>
       </c>
-      <c r="B19" s="388" t="s">
+      <c r="B19" s="387" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="388" t="s">
+      <c r="C19" s="387" t="s">
         <v>156</v>
       </c>
       <c r="D19" s="245" t="s">
@@ -81245,10 +81245,10 @@
       <c r="A20" s="255">
         <v>18</v>
       </c>
-      <c r="B20" s="387" t="s">
+      <c r="B20" s="386" t="s">
         <v>2424</v>
       </c>
-      <c r="C20" s="387" t="s">
+      <c r="C20" s="386" t="s">
         <v>2424</v>
       </c>
       <c r="D20" s="248" t="s">
@@ -81262,10 +81262,10 @@
       <c r="A21" s="255">
         <v>19</v>
       </c>
-      <c r="B21" s="388" t="s">
+      <c r="B21" s="387" t="s">
         <v>1218</v>
       </c>
-      <c r="C21" s="388" t="s">
+      <c r="C21" s="387" t="s">
         <v>1217</v>
       </c>
       <c r="D21" s="245" t="s">
@@ -81279,10 +81279,10 @@
       <c r="A22" s="255">
         <v>20</v>
       </c>
-      <c r="B22" s="387" t="s">
+      <c r="B22" s="386" t="s">
         <v>717</v>
       </c>
-      <c r="C22" s="387" t="s">
+      <c r="C22" s="386" t="s">
         <v>742</v>
       </c>
       <c r="D22" s="248" t="s">
@@ -81296,10 +81296,10 @@
       <c r="A23" s="255">
         <v>21</v>
       </c>
-      <c r="B23" s="388" t="s">
+      <c r="B23" s="387" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="388" t="s">
+      <c r="C23" s="387" t="s">
         <v>244</v>
       </c>
       <c r="D23" s="245" t="s">
@@ -81313,10 +81313,10 @@
       <c r="A24" s="255">
         <v>22</v>
       </c>
-      <c r="B24" s="387" t="s">
+      <c r="B24" s="386" t="s">
         <v>2408</v>
       </c>
-      <c r="C24" s="387" t="s">
+      <c r="C24" s="386" t="s">
         <v>2515</v>
       </c>
       <c r="D24" s="248" t="s">
@@ -81330,10 +81330,10 @@
       <c r="A25" s="255">
         <v>23</v>
       </c>
-      <c r="B25" s="388" t="s">
+      <c r="B25" s="387" t="s">
         <v>2407</v>
       </c>
-      <c r="C25" s="388" t="s">
+      <c r="C25" s="387" t="s">
         <v>2515</v>
       </c>
       <c r="D25" s="245" t="s">
@@ -81347,10 +81347,10 @@
       <c r="A26" s="255">
         <v>24</v>
       </c>
-      <c r="B26" s="387" t="s">
+      <c r="B26" s="386" t="s">
         <v>405</v>
       </c>
-      <c r="C26" s="387" t="s">
+      <c r="C26" s="386" t="s">
         <v>1155</v>
       </c>
       <c r="D26" s="248" t="s">
@@ -81364,10 +81364,10 @@
       <c r="A27" s="255">
         <v>25</v>
       </c>
-      <c r="B27" s="388" t="s">
+      <c r="B27" s="387" t="s">
         <v>1994</v>
       </c>
-      <c r="C27" s="388" t="s">
+      <c r="C27" s="387" t="s">
         <v>1994</v>
       </c>
       <c r="D27" s="245" t="s">
@@ -81381,10 +81381,10 @@
       <c r="A28" s="255">
         <v>26</v>
       </c>
-      <c r="B28" s="387" t="s">
+      <c r="B28" s="386" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="387" t="s">
+      <c r="C28" s="386" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="248" t="s">
@@ -81398,10 +81398,10 @@
       <c r="A29" s="255">
         <v>27</v>
       </c>
-      <c r="B29" s="388" t="s">
+      <c r="B29" s="387" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="388" t="s">
+      <c r="C29" s="387" t="s">
         <v>260</v>
       </c>
       <c r="D29" s="245" t="s">
@@ -81415,10 +81415,10 @@
       <c r="A30" s="255">
         <v>28</v>
       </c>
-      <c r="B30" s="387" t="s">
+      <c r="B30" s="386" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="387" t="s">
+      <c r="C30" s="386" t="s">
         <v>260</v>
       </c>
       <c r="D30" s="248" t="s">
@@ -81432,10 +81432,10 @@
       <c r="A31" s="255">
         <v>29</v>
       </c>
-      <c r="B31" s="388" t="s">
+      <c r="B31" s="387" t="s">
         <v>984</v>
       </c>
-      <c r="C31" s="388" t="s">
+      <c r="C31" s="387" t="s">
         <v>980</v>
       </c>
       <c r="D31" s="245" t="s">
@@ -81449,10 +81449,10 @@
       <c r="A32" s="255">
         <v>30</v>
       </c>
-      <c r="B32" s="387" t="s">
+      <c r="B32" s="386" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="387" t="s">
+      <c r="C32" s="386" t="s">
         <v>186</v>
       </c>
       <c r="D32" s="248" t="s">
@@ -81466,10 +81466,10 @@
       <c r="A33" s="255">
         <v>31</v>
       </c>
-      <c r="B33" s="388" t="s">
+      <c r="B33" s="387" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="388" t="s">
+      <c r="C33" s="387" t="s">
         <v>131</v>
       </c>
       <c r="D33" s="245" t="s">
@@ -81483,10 +81483,10 @@
       <c r="A34" s="255">
         <v>32</v>
       </c>
-      <c r="B34" s="387" t="s">
+      <c r="B34" s="386" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="387" t="s">
+      <c r="C34" s="386" t="s">
         <v>36</v>
       </c>
       <c r="D34" s="248" t="s">
@@ -81500,10 +81500,10 @@
       <c r="A35" s="255">
         <v>33</v>
       </c>
-      <c r="B35" s="388" t="s">
+      <c r="B35" s="387" t="s">
         <v>475</v>
       </c>
-      <c r="C35" s="388" t="s">
+      <c r="C35" s="387" t="s">
         <v>473</v>
       </c>
       <c r="D35" s="245" t="s">
@@ -81517,10 +81517,10 @@
       <c r="A36" s="255">
         <v>34</v>
       </c>
-      <c r="B36" s="387" t="s">
+      <c r="B36" s="386" t="s">
         <v>670</v>
       </c>
-      <c r="C36" s="387" t="s">
+      <c r="C36" s="386" t="s">
         <v>668</v>
       </c>
       <c r="D36" s="248" t="s">
@@ -81534,10 +81534,10 @@
       <c r="A37" s="255">
         <v>35</v>
       </c>
-      <c r="B37" s="388" t="s">
+      <c r="B37" s="387" t="s">
         <v>2503</v>
       </c>
-      <c r="C37" s="388" t="s">
+      <c r="C37" s="387" t="s">
         <v>2514</v>
       </c>
       <c r="D37" s="245" t="s">
@@ -81551,10 +81551,10 @@
       <c r="A38" s="255">
         <v>36</v>
       </c>
-      <c r="B38" s="387" t="s">
+      <c r="B38" s="386" t="s">
         <v>409</v>
       </c>
-      <c r="C38" s="387" t="s">
+      <c r="C38" s="386" t="s">
         <v>407</v>
       </c>
       <c r="D38" s="248" t="s">
@@ -81568,10 +81568,10 @@
       <c r="A39" s="255">
         <v>37</v>
       </c>
-      <c r="B39" s="388" t="s">
+      <c r="B39" s="387" t="s">
         <v>879</v>
       </c>
-      <c r="C39" s="388" t="s">
+      <c r="C39" s="387" t="s">
         <v>874</v>
       </c>
       <c r="D39" s="245" t="s">
@@ -81585,10 +81585,10 @@
       <c r="A40" s="255">
         <v>38</v>
       </c>
-      <c r="B40" s="387" t="s">
+      <c r="B40" s="386" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="387" t="s">
+      <c r="C40" s="386" t="s">
         <v>157</v>
       </c>
       <c r="D40" s="248" t="s">
@@ -81602,10 +81602,10 @@
       <c r="A41" s="255">
         <v>39</v>
       </c>
-      <c r="B41" s="388" t="s">
+      <c r="B41" s="387" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="388" t="s">
+      <c r="C41" s="387" t="s">
         <v>234</v>
       </c>
       <c r="D41" s="245" t="s">
@@ -81619,10 +81619,10 @@
       <c r="A42" s="255">
         <v>40</v>
       </c>
-      <c r="B42" s="387" t="s">
+      <c r="B42" s="386" t="s">
         <v>1103</v>
       </c>
-      <c r="C42" s="387" t="s">
+      <c r="C42" s="386" t="s">
         <v>1101</v>
       </c>
       <c r="D42" s="248" t="s">
@@ -81636,10 +81636,10 @@
       <c r="A43" s="255">
         <v>41</v>
       </c>
-      <c r="B43" s="388" t="s">
+      <c r="B43" s="387" t="s">
         <v>627</v>
       </c>
-      <c r="C43" s="388" t="s">
+      <c r="C43" s="387" t="s">
         <v>624</v>
       </c>
       <c r="D43" s="245" t="s">
@@ -81653,10 +81653,10 @@
       <c r="A44" s="255">
         <v>42</v>
       </c>
-      <c r="B44" s="387" t="s">
+      <c r="B44" s="386" t="s">
         <v>934</v>
       </c>
-      <c r="C44" s="387" t="s">
+      <c r="C44" s="386" t="s">
         <v>942</v>
       </c>
       <c r="D44" s="248" t="s">
@@ -81670,10 +81670,10 @@
       <c r="A45" s="255">
         <v>43</v>
       </c>
-      <c r="B45" s="388" t="s">
+      <c r="B45" s="387" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="388" t="s">
+      <c r="C45" s="387" t="s">
         <v>95</v>
       </c>
       <c r="D45" s="245" t="s">
@@ -81687,10 +81687,10 @@
       <c r="A46" s="255">
         <v>44</v>
       </c>
-      <c r="B46" s="387" t="s">
+      <c r="B46" s="386" t="s">
         <v>2897</v>
       </c>
-      <c r="C46" s="387" t="s">
+      <c r="C46" s="386" t="s">
         <v>2907</v>
       </c>
       <c r="D46" s="248" t="s">
@@ -81704,10 +81704,10 @@
       <c r="A47" s="255">
         <v>45</v>
       </c>
-      <c r="B47" s="388" t="s">
+      <c r="B47" s="387" t="s">
         <v>2900</v>
       </c>
-      <c r="C47" s="388" t="s">
+      <c r="C47" s="387" t="s">
         <v>2907</v>
       </c>
       <c r="D47" s="245" t="s">
@@ -81721,10 +81721,10 @@
       <c r="A48" s="255">
         <v>46</v>
       </c>
-      <c r="B48" s="387" t="s">
+      <c r="B48" s="386" t="s">
         <v>1503</v>
       </c>
-      <c r="C48" s="387" t="s">
+      <c r="C48" s="386" t="s">
         <v>1526</v>
       </c>
       <c r="D48" s="248" t="s">
@@ -81738,10 +81738,10 @@
       <c r="A49" s="255">
         <v>47</v>
       </c>
-      <c r="B49" s="388" t="s">
+      <c r="B49" s="387" t="s">
         <v>1505</v>
       </c>
-      <c r="C49" s="388" t="s">
+      <c r="C49" s="387" t="s">
         <v>1526</v>
       </c>
       <c r="D49" s="245" t="s">
@@ -81755,10 +81755,10 @@
       <c r="A50" s="255">
         <v>48</v>
       </c>
-      <c r="B50" s="387" t="s">
+      <c r="B50" s="386" t="s">
         <v>2339</v>
       </c>
-      <c r="C50" s="387" t="s">
+      <c r="C50" s="386" t="s">
         <v>2349</v>
       </c>
       <c r="D50" s="248" t="s">
@@ -81772,10 +81772,10 @@
       <c r="A51" s="255">
         <v>49</v>
       </c>
-      <c r="B51" s="388" t="s">
+      <c r="B51" s="387" t="s">
         <v>2812</v>
       </c>
-      <c r="C51" s="388" t="s">
+      <c r="C51" s="387" t="s">
         <v>2818</v>
       </c>
       <c r="D51" s="245" t="s">
@@ -81789,10 +81789,10 @@
       <c r="A52" s="255">
         <v>50</v>
       </c>
-      <c r="B52" s="387" t="s">
+      <c r="B52" s="386" t="s">
         <v>2820</v>
       </c>
-      <c r="C52" s="387" t="s">
+      <c r="C52" s="386" t="s">
         <v>2818</v>
       </c>
       <c r="D52" s="248" t="s">
@@ -81806,10 +81806,10 @@
       <c r="A53" s="255">
         <v>51</v>
       </c>
-      <c r="B53" s="388" t="s">
+      <c r="B53" s="387" t="s">
         <v>1778</v>
       </c>
-      <c r="C53" s="388" t="s">
+      <c r="C53" s="387" t="s">
         <v>1779</v>
       </c>
       <c r="D53" s="245" t="s">
@@ -81823,10 +81823,10 @@
       <c r="A54" s="255">
         <v>52</v>
       </c>
-      <c r="B54" s="387" t="s">
+      <c r="B54" s="386" t="s">
         <v>2959</v>
       </c>
-      <c r="C54" s="387" t="s">
+      <c r="C54" s="386" t="s">
         <v>2981</v>
       </c>
       <c r="D54" s="248" t="s">
@@ -81840,10 +81840,10 @@
       <c r="A55" s="255">
         <v>53</v>
       </c>
-      <c r="B55" s="388" t="s">
+      <c r="B55" s="387" t="s">
         <v>2973</v>
       </c>
-      <c r="C55" s="388" t="s">
+      <c r="C55" s="387" t="s">
         <v>2981</v>
       </c>
       <c r="D55" s="245" t="s">
@@ -81857,10 +81857,10 @@
       <c r="A56" s="255">
         <v>54</v>
       </c>
-      <c r="B56" s="387" t="s">
+      <c r="B56" s="386" t="s">
         <v>1589</v>
       </c>
-      <c r="C56" s="387" t="s">
+      <c r="C56" s="386" t="s">
         <v>1590</v>
       </c>
       <c r="D56" s="248" t="s">
@@ -81874,10 +81874,10 @@
       <c r="A57" s="255">
         <v>55</v>
       </c>
-      <c r="B57" s="388" t="s">
+      <c r="B57" s="387" t="s">
         <v>706</v>
       </c>
-      <c r="C57" s="388" t="s">
+      <c r="C57" s="387" t="s">
         <v>715</v>
       </c>
       <c r="D57" s="245" t="s">
@@ -81891,10 +81891,10 @@
       <c r="A58" s="255">
         <v>56</v>
       </c>
-      <c r="B58" s="387" t="s">
+      <c r="B58" s="386" t="s">
         <v>2029</v>
       </c>
-      <c r="C58" s="387" t="s">
+      <c r="C58" s="386" t="s">
         <v>2057</v>
       </c>
       <c r="D58" s="248" t="s">
@@ -81908,10 +81908,10 @@
       <c r="A59" s="255">
         <v>57</v>
       </c>
-      <c r="B59" s="388" t="s">
+      <c r="B59" s="387" t="s">
         <v>2040</v>
       </c>
-      <c r="C59" s="388" t="s">
+      <c r="C59" s="387" t="s">
         <v>2057</v>
       </c>
       <c r="D59" s="245" t="s">
@@ -81925,10 +81925,10 @@
       <c r="A60" s="255">
         <v>58</v>
       </c>
-      <c r="B60" s="387" t="s">
+      <c r="B60" s="386" t="s">
         <v>2493</v>
       </c>
-      <c r="C60" s="387" t="s">
+      <c r="C60" s="386" t="s">
         <v>2493</v>
       </c>
       <c r="D60" s="248" t="s">
@@ -81942,10 +81942,10 @@
       <c r="A61" s="255">
         <v>59</v>
       </c>
-      <c r="B61" s="388" t="s">
+      <c r="B61" s="387" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="388" t="s">
+      <c r="C61" s="387" t="s">
         <v>1156</v>
       </c>
       <c r="D61" s="245" t="s">
@@ -81959,10 +81959,10 @@
       <c r="A62" s="255">
         <v>60</v>
       </c>
-      <c r="B62" s="387" t="s">
+      <c r="B62" s="386" t="s">
         <v>1131</v>
       </c>
-      <c r="C62" s="387" t="s">
+      <c r="C62" s="386" t="s">
         <v>1524</v>
       </c>
       <c r="D62" s="248" t="s">
@@ -81976,10 +81976,10 @@
       <c r="A63" s="255">
         <v>61</v>
       </c>
-      <c r="B63" s="388" t="s">
+      <c r="B63" s="387" t="s">
         <v>1137</v>
       </c>
-      <c r="C63" s="388" t="s">
+      <c r="C63" s="387" t="s">
         <v>1524</v>
       </c>
       <c r="D63" s="245" t="s">
@@ -81993,10 +81993,10 @@
       <c r="A64" s="255">
         <v>62</v>
       </c>
-      <c r="B64" s="387" t="s">
+      <c r="B64" s="386" t="s">
         <v>1392</v>
       </c>
-      <c r="C64" s="387" t="s">
+      <c r="C64" s="386" t="s">
         <v>1401</v>
       </c>
       <c r="D64" s="248" t="s">
@@ -82010,10 +82010,10 @@
       <c r="A65" s="255">
         <v>63</v>
       </c>
-      <c r="B65" s="388" t="s">
+      <c r="B65" s="387" t="s">
         <v>1333</v>
       </c>
-      <c r="C65" s="388" t="s">
+      <c r="C65" s="387" t="s">
         <v>1348</v>
       </c>
       <c r="D65" s="245" t="s">
@@ -82027,10 +82027,10 @@
       <c r="A66" s="255">
         <v>64</v>
       </c>
-      <c r="B66" s="387" t="s">
+      <c r="B66" s="386" t="s">
         <v>2527</v>
       </c>
-      <c r="C66" s="387" t="s">
+      <c r="C66" s="386" t="s">
         <v>2536</v>
       </c>
       <c r="D66" s="248" t="s">
@@ -82044,10 +82044,10 @@
       <c r="A67" s="255">
         <v>65</v>
       </c>
-      <c r="B67" s="388" t="s">
+      <c r="B67" s="387" t="s">
         <v>3136</v>
       </c>
-      <c r="C67" s="388" t="s">
+      <c r="C67" s="387" t="s">
         <v>3128</v>
       </c>
       <c r="D67" s="245" t="s">
@@ -82061,10 +82061,10 @@
       <c r="A68" s="255">
         <v>66</v>
       </c>
-      <c r="B68" s="387" t="s">
+      <c r="B68" s="386" t="s">
         <v>1178</v>
       </c>
-      <c r="C68" s="387" t="s">
+      <c r="C68" s="386" t="s">
         <v>316</v>
       </c>
       <c r="D68" s="248" t="s">
@@ -82078,10 +82078,10 @@
       <c r="A69" s="255">
         <v>67</v>
       </c>
-      <c r="B69" s="388" t="s">
+      <c r="B69" s="387" t="s">
         <v>2473</v>
       </c>
-      <c r="C69" s="388" t="s">
+      <c r="C69" s="387" t="s">
         <v>2461</v>
       </c>
       <c r="D69" s="245" t="s">
@@ -82095,10 +82095,10 @@
       <c r="A70" s="255">
         <v>68</v>
       </c>
-      <c r="B70" s="387" t="s">
+      <c r="B70" s="386" t="s">
         <v>962</v>
       </c>
-      <c r="C70" s="387" t="s">
+      <c r="C70" s="386" t="s">
         <v>967</v>
       </c>
       <c r="D70" s="248" t="s">
@@ -82112,10 +82112,10 @@
       <c r="A71" s="255">
         <v>69</v>
       </c>
-      <c r="B71" s="388" t="s">
+      <c r="B71" s="387" t="s">
         <v>1488</v>
       </c>
-      <c r="C71" s="388" t="s">
+      <c r="C71" s="387" t="s">
         <v>1496</v>
       </c>
       <c r="D71" s="245" t="s">
@@ -82129,10 +82129,10 @@
       <c r="A72" s="255">
         <v>70</v>
       </c>
-      <c r="B72" s="387" t="s">
+      <c r="B72" s="386" t="s">
         <v>2082</v>
       </c>
-      <c r="C72" s="387" t="s">
+      <c r="C72" s="386" t="s">
         <v>2083</v>
       </c>
       <c r="D72" s="248" t="s">
@@ -82146,10 +82146,10 @@
       <c r="A73" s="255">
         <v>71</v>
       </c>
-      <c r="B73" s="388" t="s">
+      <c r="B73" s="387" t="s">
         <v>2296</v>
       </c>
-      <c r="C73" s="388" t="s">
+      <c r="C73" s="387" t="s">
         <v>2307</v>
       </c>
       <c r="D73" s="245" t="s">
@@ -82163,10 +82163,10 @@
       <c r="A74" s="255">
         <v>72</v>
       </c>
-      <c r="B74" s="387" t="s">
+      <c r="B74" s="386" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="387" t="s">
+      <c r="C74" s="386" t="s">
         <v>365</v>
       </c>
       <c r="D74" s="248" t="s">
@@ -82180,10 +82180,10 @@
       <c r="A75" s="255">
         <v>73</v>
       </c>
-      <c r="B75" s="388" t="s">
+      <c r="B75" s="387" t="s">
         <v>443</v>
       </c>
-      <c r="C75" s="388" t="s">
+      <c r="C75" s="387" t="s">
         <v>456</v>
       </c>
       <c r="D75" s="245" t="s">
@@ -82197,10 +82197,10 @@
       <c r="A76" s="255">
         <v>74</v>
       </c>
-      <c r="B76" s="387" t="s">
+      <c r="B76" s="386" t="s">
         <v>2847</v>
       </c>
-      <c r="C76" s="387" t="s">
+      <c r="C76" s="386" t="s">
         <v>2850</v>
       </c>
       <c r="D76" s="248" t="s">
@@ -82214,10 +82214,10 @@
       <c r="A77" s="255">
         <v>75</v>
       </c>
-      <c r="B77" s="388" t="s">
+      <c r="B77" s="387" t="s">
         <v>559</v>
       </c>
-      <c r="C77" s="388" t="s">
+      <c r="C77" s="387" t="s">
         <v>561</v>
       </c>
       <c r="D77" s="245" t="s">
@@ -82231,10 +82231,10 @@
       <c r="A78" s="255">
         <v>76</v>
       </c>
-      <c r="B78" s="387" t="s">
+      <c r="B78" s="386" t="s">
         <v>596</v>
       </c>
-      <c r="C78" s="387" t="s">
+      <c r="C78" s="386" t="s">
         <v>603</v>
       </c>
       <c r="D78" s="248" t="s">
@@ -82248,10 +82248,10 @@
       <c r="A79" s="255">
         <v>77</v>
       </c>
-      <c r="B79" s="388" t="s">
+      <c r="B79" s="387" t="s">
         <v>1246</v>
       </c>
-      <c r="C79" s="388" t="s">
+      <c r="C79" s="387" t="s">
         <v>1254</v>
       </c>
       <c r="D79" s="245" t="s">
@@ -82265,10 +82265,10 @@
       <c r="A80" s="255">
         <v>78</v>
       </c>
-      <c r="B80" s="387" t="s">
+      <c r="B80" s="386" t="s">
         <v>871</v>
       </c>
-      <c r="C80" s="387" t="s">
+      <c r="C80" s="386" t="s">
         <v>872</v>
       </c>
       <c r="D80" s="248" t="s">
@@ -82282,10 +82282,10 @@
       <c r="A81" s="255">
         <v>79</v>
       </c>
-      <c r="B81" s="388" t="s">
+      <c r="B81" s="387" t="s">
         <v>2480</v>
       </c>
-      <c r="C81" s="388" t="s">
+      <c r="C81" s="387" t="s">
         <v>2477</v>
       </c>
       <c r="D81" s="245" t="s">
@@ -82299,10 +82299,10 @@
       <c r="A82" s="255">
         <v>80</v>
       </c>
-      <c r="B82" s="387" t="s">
+      <c r="B82" s="386" t="s">
         <v>802</v>
       </c>
-      <c r="C82" s="387" t="s">
+      <c r="C82" s="386" t="s">
         <v>807</v>
       </c>
       <c r="D82" s="248" t="s">
@@ -82316,10 +82316,10 @@
       <c r="A83" s="255">
         <v>81</v>
       </c>
-      <c r="B83" s="388" t="s">
+      <c r="B83" s="387" t="s">
         <v>1451</v>
       </c>
-      <c r="C83" s="388" t="s">
+      <c r="C83" s="387" t="s">
         <v>1453</v>
       </c>
       <c r="D83" s="245" t="s">
@@ -82333,10 +82333,10 @@
       <c r="A84" s="255">
         <v>82</v>
       </c>
-      <c r="B84" s="387" t="s">
+      <c r="B84" s="386" t="s">
         <v>682</v>
       </c>
-      <c r="C84" s="387" t="s">
+      <c r="C84" s="386" t="s">
         <v>688</v>
       </c>
       <c r="D84" s="248" t="s">
@@ -82350,10 +82350,10 @@
       <c r="A85" s="255">
         <v>83</v>
       </c>
-      <c r="B85" s="388" t="s">
+      <c r="B85" s="387" t="s">
         <v>685</v>
       </c>
-      <c r="C85" s="388" t="s">
+      <c r="C85" s="387" t="s">
         <v>688</v>
       </c>
       <c r="D85" s="245" t="s">
@@ -82367,10 +82367,10 @@
       <c r="A86" s="255">
         <v>84</v>
       </c>
-      <c r="B86" s="387" t="s">
+      <c r="B86" s="386" t="s">
         <v>378</v>
       </c>
-      <c r="C86" s="387" t="s">
+      <c r="C86" s="386" t="s">
         <v>382</v>
       </c>
       <c r="D86" s="248" t="s">
@@ -82384,10 +82384,10 @@
       <c r="A87" s="255">
         <v>85</v>
       </c>
-      <c r="B87" s="388" t="s">
+      <c r="B87" s="387" t="s">
         <v>2550</v>
       </c>
-      <c r="C87" s="388" t="s">
+      <c r="C87" s="387" t="s">
         <v>2573</v>
       </c>
       <c r="D87" s="245" t="s">
@@ -82401,10 +82401,10 @@
       <c r="A88" s="255">
         <v>86</v>
       </c>
-      <c r="B88" s="387" t="s">
+      <c r="B88" s="386" t="s">
         <v>1320</v>
       </c>
-      <c r="C88" s="387" t="s">
+      <c r="C88" s="386" t="s">
         <v>310</v>
       </c>
       <c r="D88" s="248" t="s">
@@ -82418,10 +82418,10 @@
       <c r="A89" s="255">
         <v>87</v>
       </c>
-      <c r="B89" s="388" t="s">
+      <c r="B89" s="387" t="s">
         <v>1324</v>
       </c>
-      <c r="C89" s="388" t="s">
+      <c r="C89" s="387" t="s">
         <v>310</v>
       </c>
       <c r="D89" s="245" t="s">
@@ -82435,10 +82435,10 @@
       <c r="A90" s="255">
         <v>88</v>
       </c>
-      <c r="B90" s="387" t="s">
+      <c r="B90" s="386" t="s">
         <v>3272</v>
       </c>
-      <c r="C90" s="387" t="s">
+      <c r="C90" s="386" t="s">
         <v>1676</v>
       </c>
       <c r="D90" s="248" t="s">
@@ -82452,10 +82452,10 @@
       <c r="A91" s="255">
         <v>89</v>
       </c>
-      <c r="B91" s="388" t="s">
+      <c r="B91" s="387" t="s">
         <v>905</v>
       </c>
-      <c r="C91" s="388" t="s">
+      <c r="C91" s="387" t="s">
         <v>887</v>
       </c>
       <c r="D91" s="245" t="s">
@@ -82469,10 +82469,10 @@
       <c r="A92" s="255">
         <v>90</v>
       </c>
-      <c r="B92" s="387" t="s">
+      <c r="B92" s="386" t="s">
         <v>3086</v>
       </c>
-      <c r="C92" s="387" t="s">
+      <c r="C92" s="386" t="s">
         <v>3276</v>
       </c>
       <c r="D92" s="248" t="s">
@@ -82486,10 +82486,10 @@
       <c r="A93" s="255">
         <v>91</v>
       </c>
-      <c r="B93" s="388" t="s">
+      <c r="B93" s="387" t="s">
         <v>824</v>
       </c>
-      <c r="C93" s="388" t="s">
+      <c r="C93" s="387" t="s">
         <v>830</v>
       </c>
       <c r="D93" s="245" t="s">
@@ -82503,10 +82503,10 @@
       <c r="A94" s="255">
         <v>92</v>
       </c>
-      <c r="B94" s="387" t="s">
+      <c r="B94" s="386" t="s">
         <v>2362</v>
       </c>
-      <c r="C94" s="387" t="s">
+      <c r="C94" s="386" t="s">
         <v>2366</v>
       </c>
       <c r="D94" s="248" t="s">
@@ -82520,10 +82520,10 @@
       <c r="A95" s="255">
         <v>93</v>
       </c>
-      <c r="B95" s="388" t="s">
+      <c r="B95" s="387" t="s">
         <v>2061</v>
       </c>
-      <c r="C95" s="388" t="s">
+      <c r="C95" s="387" t="s">
         <v>2071</v>
       </c>
       <c r="D95" s="245" t="s">
@@ -82537,10 +82537,10 @@
       <c r="A96" s="255">
         <v>94</v>
       </c>
-      <c r="B96" s="387" t="s">
+      <c r="B96" s="386" t="s">
         <v>2775</v>
       </c>
-      <c r="C96" s="387" t="s">
+      <c r="C96" s="386" t="s">
         <v>2782</v>
       </c>
       <c r="D96" s="248" t="s">
@@ -82554,10 +82554,10 @@
       <c r="A97" s="255">
         <v>95</v>
       </c>
-      <c r="B97" s="388" t="s">
+      <c r="B97" s="387" t="s">
         <v>2943</v>
       </c>
-      <c r="C97" s="388" t="s">
+      <c r="C97" s="387" t="s">
         <v>2952</v>
       </c>
       <c r="D97" s="245" t="s">
@@ -82571,10 +82571,10 @@
       <c r="A98" s="255">
         <v>96</v>
       </c>
-      <c r="B98" s="387" t="s">
+      <c r="B98" s="386" t="s">
         <v>2608</v>
       </c>
-      <c r="C98" s="387" t="s">
+      <c r="C98" s="386" t="s">
         <v>692</v>
       </c>
       <c r="D98" s="248" t="s">
@@ -82588,10 +82588,10 @@
       <c r="A99" s="255">
         <v>97</v>
       </c>
-      <c r="B99" s="388" t="s">
+      <c r="B99" s="387" t="s">
         <v>578</v>
       </c>
-      <c r="C99" s="388" t="s">
+      <c r="C99" s="387" t="s">
         <v>588</v>
       </c>
       <c r="D99" s="245" t="s">
